--- a/results/Brazil-National-FREL-Results_V1/0_brazil_national_frel_results_v1.xlsx
+++ b/results/Brazil-National-FREL-Results_V1/0_brazil_national_frel_results_v1.xlsx
@@ -1,27 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Celso\Documents\GitHub\Brazil-National-FREL\results\Brazil-National-FREL-Results_V1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ipamamazonia-my.sharepoint.com/personal/celso_junior_ipam_org_br/Documents/Documentos/GitHub/Brazil-National-FREL/results/Brazil-National-FREL-Results_V1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF1CDFEF-10C2-4160-B838-8A2CD3DC1914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{FF1CDFEF-10C2-4160-B838-8A2CD3DC1914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B838970D-C506-4B25-ACF5-D9A4BC3AAF49}"/>
   <bookViews>
-    <workbookView xWindow="2160" yWindow="2160" windowWidth="21000" windowHeight="12855" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-105" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
-    <sheet name="Planilha1" sheetId="2" r:id="rId2"/>
-    <sheet name="Planilha2" sheetId="3" r:id="rId3"/>
+    <sheet name="Dataset" sheetId="1" r:id="rId1"/>
+    <sheet name="Pivot Table" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="10" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3666" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3652" uniqueCount="49">
   <si>
     <t>biome</t>
   </si>
@@ -187,67 +185,18 @@
   <si>
     <t>Soma de emission_tco2eq</t>
   </si>
-  <si>
-    <t>Emission Source</t>
-  </si>
-  <si>
-    <t>Average (2017-2021) of official emissions</t>
-  </si>
-  <si>
-    <t>(t CO₂ eq)</t>
-  </si>
-  <si>
-    <t>Estimated Emission in 2022</t>
-  </si>
-  <si>
-    <t>Estimated Emission in 2023</t>
-  </si>
-  <si>
-    <t>Estimated Result for 2022</t>
-  </si>
-  <si>
-    <t>Estimated Result for 2023</t>
-  </si>
-  <si>
-    <t>Net Deforestation</t>
-  </si>
-  <si>
-    <t>Fire</t>
-  </si>
-  <si>
-    <t>Selective Logging</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -258,7 +207,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -266,90 +215,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -370,7 +246,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Celso H. L. Silva Junior" refreshedDate="45811.86141041667" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="903" xr:uid="{52301A32-0D38-4190-80B9-5B06171F2375}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:F904" sheet="Sheet 1"/>
+    <worksheetSource ref="A1:F904" sheet="Dataset"/>
   </cacheSource>
   <cacheFields count="6">
     <cacheField name="biome" numFmtId="0">
@@ -7653,112 +7529,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0559D85D-6E27-4059-BDD1-1C6021A484B4}" name="Tabela dinâmica4" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A33:C42" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="6">
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
-        <item h="1" x="4"/>
-        <item h="1" x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="4">
-        <item h="1" x="0"/>
-        <item h="1" x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="8">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="8">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="3"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="0" hier="-1"/>
-    <pageField fld="2" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Soma de emission_tco2eq" fld="5" baseField="4" baseItem="0" numFmtId="3"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E55AE87B-8622-484F-9061-221DA0F8C1EA}" name="Tabela dinâmica3" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E55AE87B-8622-484F-9061-221DA0F8C1EA}" name="Tabela dinâmica3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A19:E28" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="6">
     <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
@@ -7868,8 +7639,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E7EE9004-1FFA-4660-9D25-8C6BB875F62E}" name="Tabela dinâmica1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E7EE9004-1FFA-4660-9D25-8C6BB875F62E}" name="Tabela dinâmica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:E13" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="6">
     <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
@@ -7955,6 +7726,111 @@
     </i>
     <i>
       <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="0" hier="-1"/>
+    <pageField fld="2" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Soma de emission_tco2eq" fld="5" baseField="4" baseItem="0" numFmtId="3"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0559D85D-6E27-4059-BDD1-1C6021A484B4}" name="Tabela dinâmica4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A33:C42" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="6">
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item h="1" x="4"/>
+        <item h="1" x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="4">
+        <item h="1" x="0"/>
+        <item h="1" x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="8">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="3"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="1"/>
     </i>
     <i t="grand">
       <x/>
@@ -8259,12 +8135,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F904"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="6" max="6" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8284,7 +8160,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -8304,7 +8180,7 @@
         <v>1749316.0330042499</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -8324,7 +8200,7 @@
         <v>295389.31329575297</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -8344,7 +8220,7 @@
         <v>1973076.1095291199</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -8364,7 +8240,7 @@
         <v>476530.86779113498</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -8384,7 +8260,7 @@
         <v>2015863.06656998</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -8404,7 +8280,7 @@
         <v>198209.974942498</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -8424,7 +8300,7 @@
         <v>4541732.2524984796</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -8444,7 +8320,7 @@
         <v>82831.658709769399</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -8464,7 +8340,7 @@
         <v>14155.8948531102</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -8484,7 +8360,7 @@
         <v>1854032.8587078899</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -8504,7 +8380,7 @@
         <v>170513.36329383799</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -8524,7 +8400,7 @@
         <v>1951666.0458718999</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -8544,7 +8420,7 @@
         <v>841121.88906920701</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -8564,7 +8440,7 @@
         <v>2163431.1410830701</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -8584,7 +8460,7 @@
         <v>202383.14947598899</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -8604,7 +8480,7 @@
         <v>4417833.8020179402</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -8624,7 +8500,7 @@
         <v>78840.036970132307</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -8644,7 +8520,7 @@
         <v>7147.9182227126303</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -8664,7 +8540,7 @@
         <v>2372815.6604018002</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -8684,7 +8560,7 @@
         <v>246837.814289225</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -8704,7 +8580,7 @@
         <v>2234562.5581184002</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -8724,7 +8600,7 @@
         <v>1384732.1602046001</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -8744,7 +8620,7 @@
         <v>3161362.8523810999</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -8764,7 +8640,7 @@
         <v>778953.93098302896</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -8784,7 +8660,7 @@
         <v>7453705.3807908902</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -8804,7 +8680,7 @@
         <v>126559.86053107301</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -8824,7 +8700,7 @@
         <v>12301.2239139433</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -8844,7 +8720,7 @@
         <v>2222545.8757255501</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -8864,7 +8740,7 @@
         <v>349661.06794007902</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -8884,7 +8760,7 @@
         <v>2129076.9779252</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -8904,7 +8780,7 @@
         <v>1396357.0448640001</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -8924,7 +8800,7 @@
         <v>2952201.67861471</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -8944,7 +8820,7 @@
         <v>497829.40099275002</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -8964,7 +8840,7 @@
         <v>7517778.72120832</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -8984,7 +8860,7 @@
         <v>43984.507912784698</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>6</v>
       </c>
@@ -9004,7 +8880,7 @@
         <v>10070.819515253501</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -9024,7 +8900,7 @@
         <v>2548964.3325276198</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -9044,7 +8920,7 @@
         <v>270131.92151912098</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -9064,7 +8940,7 @@
         <v>2743535.96773885</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -9084,7 +8960,7 @@
         <v>1785327.8319465599</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -9104,7 +8980,7 @@
         <v>4396742.3489817902</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>6</v>
       </c>
@@ -9124,7 +9000,7 @@
         <v>440335.49886657199</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>6</v>
       </c>
@@ -9144,7 +9020,7 @@
         <v>8675335.2557675</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>6</v>
       </c>
@@ -9164,7 +9040,7 @@
         <v>54135.152710830298</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>6</v>
       </c>
@@ -9184,7 +9060,7 @@
         <v>13659.766067024</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>6</v>
       </c>
@@ -9204,7 +9080,7 @@
         <v>2678893.7791158301</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>6</v>
       </c>
@@ -9224,7 +9100,7 @@
         <v>191027.75225934701</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -9244,7 +9120,7 @@
         <v>2490938.47841118</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>6</v>
       </c>
@@ -9264,7 +9140,7 @@
         <v>2103669.5957044102</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>6</v>
       </c>
@@ -9284,7 +9160,7 @@
         <v>6231651.3758057496</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>6</v>
       </c>
@@ -9304,7 +9180,7 @@
         <v>460898.199880081</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>6</v>
       </c>
@@ -9324,7 +9200,7 @@
         <v>7811301.4110270496</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>6</v>
       </c>
@@ -9344,7 +9220,7 @@
         <v>29699.073986576801</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -9364,7 +9240,7 @@
         <v>14640.0965208178</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>6</v>
       </c>
@@ -9384,7 +9260,7 @@
         <v>2317425.0852602799</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>6</v>
       </c>
@@ -9404,7 +9280,7 @@
         <v>231381.50259875401</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>6</v>
       </c>
@@ -9424,7 +9300,7 @@
         <v>1364823.97842452</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -9444,7 +9320,7 @@
         <v>1106594.5081589201</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>6</v>
       </c>
@@ -9464,7 +9340,7 @@
         <v>2817163.18982876</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>6</v>
       </c>
@@ -9484,7 +9360,7 @@
         <v>493932.62031842401</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>6</v>
       </c>
@@ -9504,7 +9380,7 @@
         <v>5084246.2462360496</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>6</v>
       </c>
@@ -9524,7 +9400,7 @@
         <v>59480.462722373901</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>6</v>
       </c>
@@ -9544,7 +9420,7 @@
         <v>10037.583018921599</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>6</v>
       </c>
@@ -9564,7 +9440,7 @@
         <v>49291226.680943199</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>6</v>
       </c>
@@ -9584,7 +9460,7 @@
         <v>8970518.0401530806</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>6</v>
       </c>
@@ -9604,7 +9480,7 @@
         <v>54107851.137065701</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>6</v>
       </c>
@@ -9624,7 +9500,7 @@
         <v>13335269.9940565</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>6</v>
       </c>
@@ -9644,7 +9520,7 @@
         <v>59965090.812154301</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>6</v>
       </c>
@@ -9664,7 +9540,7 @@
         <v>5999683.4066322697</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>6</v>
       </c>
@@ -9684,7 +9560,7 @@
         <v>138097321.699577</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>6</v>
       </c>
@@ -9704,7 +9580,7 @@
         <v>2610175.0903445701</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>6</v>
       </c>
@@ -9724,7 +9600,7 @@
         <v>419961.69722933898</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>6</v>
       </c>
@@ -9744,7 +9620,7 @@
         <v>52428082.538544901</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>6</v>
       </c>
@@ -9764,7 +9640,7 @@
         <v>5214733.0606379397</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>6</v>
       </c>
@@ -9784,7 +9660,7 @@
         <v>53486042.625337198</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>6</v>
       </c>
@@ -9804,7 +9680,7 @@
         <v>23340079.869737402</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>6</v>
       </c>
@@ -9824,7 +9700,7 @@
         <v>63726414.975247703</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>6</v>
       </c>
@@ -9844,7 +9720,7 @@
         <v>6146364.4888289198</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>6</v>
       </c>
@@ -9864,7 +9740,7 @@
         <v>132539130.93012001</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>6</v>
       </c>
@@ -9884,7 +9760,7 @@
         <v>2493965.1734025101</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>6</v>
       </c>
@@ -9904,7 +9780,7 @@
         <v>207067.48843460501</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>6</v>
       </c>
@@ -9924,7 +9800,7 @@
         <v>68207381.765532702</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>6</v>
       </c>
@@ -9944,7 +9820,7 @@
         <v>7644985.0362817403</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>6</v>
       </c>
@@ -9964,7 +9840,7 @@
         <v>61173817.101613</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>6</v>
       </c>
@@ -9984,7 +9860,7 @@
         <v>38524100.5201689</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>6</v>
       </c>
@@ -10004,7 +9880,7 @@
         <v>92867129.416266397</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>6</v>
       </c>
@@ -10024,7 +9900,7 @@
         <v>23627194.598344199</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>6</v>
       </c>
@@ -10044,7 +9920,7 @@
         <v>224173785.08595201</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>6</v>
       </c>
@@ -10064,7 +9940,7 @@
         <v>3975756.7390164901</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>6</v>
       </c>
@@ -10084,7 +9960,7 @@
         <v>350041.42251741601</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>6</v>
       </c>
@@ -10104,7 +9980,7 @@
         <v>62556171.725371599</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>6</v>
       </c>
@@ -10124,7 +10000,7 @@
         <v>10453937.468634499</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>6</v>
       </c>
@@ -10144,7 +10020,7 @@
         <v>58132132.240736403</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>6</v>
       </c>
@@ -10164,7 +10040,7 @@
         <v>38653677.650201</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>6</v>
       </c>
@@ -10184,7 +10060,7 @@
         <v>87075794.177589104</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>6</v>
       </c>
@@ -10204,7 +10080,7 @@
         <v>15090261.152747201</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>6</v>
       </c>
@@ -10224,7 +10100,7 @@
         <v>224020133.40562099</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>6</v>
       </c>
@@ -10244,7 +10120,7 @@
         <v>1379941.1800669101</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>6</v>
       </c>
@@ -10264,7 +10140,7 @@
         <v>302080.26933879103</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>6</v>
       </c>
@@ -10284,7 +10160,7 @@
         <v>72251640.096140206</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>6</v>
       </c>
@@ -10304,7 +10180,7 @@
         <v>8246884.1478078403</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>6</v>
       </c>
@@ -10324,7 +10200,7 @@
         <v>75057806.665780798</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>6</v>
       </c>
@@ -10344,7 +10220,7 @@
         <v>49817936.262283102</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>6</v>
       </c>
@@ -10364,7 +10240,7 @@
         <v>128696380.47810601</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>6</v>
       </c>
@@ -10384,7 +10260,7 @@
         <v>13278495.559765</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>6</v>
       </c>
@@ -10404,7 +10280,7 @@
         <v>259635639.31295601</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>6</v>
       </c>
@@ -10424,7 +10300,7 @@
         <v>1708872.64595233</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>6</v>
       </c>
@@ -10444,7 +10320,7 @@
         <v>398327.54852667399</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>6</v>
       </c>
@@ -10464,7 +10340,7 @@
         <v>75506952.823383495</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>6</v>
       </c>
@@ -10484,7 +10360,7 @@
         <v>5928790.6941061001</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>6</v>
       </c>
@@ -10504,7 +10380,7 @@
         <v>68413090.808756098</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>6</v>
       </c>
@@ -10524,7 +10400,7 @@
         <v>58096664.902414903</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>6</v>
       </c>
@@ -10544,7 +10420,7 @@
         <v>183898710.47050899</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>6</v>
       </c>
@@ -10564,7 +10440,7 @@
         <v>14055671.228224101</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>6</v>
       </c>
@@ -10584,7 +10460,7 @@
         <v>234586840.89522099</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>6</v>
       </c>
@@ -10604,7 +10480,7 @@
         <v>938277.85694234096</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>6</v>
       </c>
@@ -10624,7 +10500,7 @@
         <v>421036.06275867298</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>6</v>
       </c>
@@ -10644,7 +10520,7 @@
         <v>65073829.584519699</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>6</v>
       </c>
@@ -10664,7 +10540,7 @@
         <v>7089681.0704783704</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>6</v>
       </c>
@@ -10684,7 +10560,7 @@
         <v>37553030.972575597</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>6</v>
       </c>
@@ -10704,7 +10580,7 @@
         <v>30701908.2466751</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>6</v>
       </c>
@@ -10724,7 +10600,7 @@
         <v>83687883.534609601</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>6</v>
       </c>
@@ -10744,7 +10620,7 @@
         <v>15127566.8955396</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>6</v>
       </c>
@@ -10764,7 +10640,7 @@
         <v>154909201.86858699</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>6</v>
       </c>
@@ -10784,7 +10660,7 @@
         <v>1882938.6762295</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>6</v>
       </c>
@@ -10804,7 +10680,7 @@
         <v>295189.31190016901</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>6</v>
       </c>
@@ -10824,7 +10700,7 @@
         <v>486941.96296859998</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>6</v>
       </c>
@@ -10844,7 +10720,7 @@
         <v>82224.966411107904</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>6</v>
       </c>
@@ -10864,7 +10740,7 @@
         <v>549228.11872399203</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>6</v>
       </c>
@@ -10884,7 +10760,7 @@
         <v>132647.773072112</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>6</v>
       </c>
@@ -10904,7 +10780,7 @@
         <v>561138.35361454496</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>6</v>
       </c>
@@ -10924,7 +10800,7 @@
         <v>55173.9951258004</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>6</v>
       </c>
@@ -10944,7 +10820,7 @@
         <v>1264242.69633624</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>6</v>
       </c>
@@ -10964,7 +10840,7 @@
         <v>23057.131888748801</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>6</v>
       </c>
@@ -10984,7 +10860,7 @@
         <v>3940.45392444769</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>6</v>
       </c>
@@ -11004,7 +10880,7 @@
         <v>516091.07936725102</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>6</v>
       </c>
@@ -11024,7 +10900,7 @@
         <v>47464.329068137697</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>6</v>
       </c>
@@ -11044,7 +10920,7 @@
         <v>543268.384617734</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>6</v>
       </c>
@@ -11064,7 +10940,7 @@
         <v>234135.81996149101</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>6</v>
       </c>
@@ -11084,7 +10960,7 @@
         <v>602215.60124686302</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>6</v>
       </c>
@@ -11104,7 +10980,7 @@
         <v>56335.645599933698</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>6</v>
       </c>
@@ -11124,7 +11000,7 @@
         <v>1229754.1570743499</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>6</v>
       </c>
@@ -11144,7 +11020,7 @@
         <v>21946.0186944171</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>6</v>
       </c>
@@ -11164,7 +11040,7 @@
         <v>1989.7041271206399</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>6</v>
       </c>
@@ -11184,7 +11060,7 @@
         <v>660500.15756986802</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>6</v>
       </c>
@@ -11204,7 +11080,7 @@
         <v>68710.105868324099</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>6</v>
       </c>
@@ -11224,7 +11100,7 @@
         <v>622015.83813169505</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>6</v>
       </c>
@@ -11244,7 +11120,7 @@
         <v>385455.90593927499</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>6</v>
       </c>
@@ -11264,7 +11140,7 @@
         <v>880001.21416074003</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>6</v>
       </c>
@@ -11284,7 +11160,7 @@
         <v>216830.66356139001</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>6</v>
       </c>
@@ -11304,7 +11180,7 @@
         <v>2074823.4515855899</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>6</v>
       </c>
@@ -11324,7 +11200,7 @@
         <v>35229.372941947702</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>6</v>
       </c>
@@ -11344,7 +11220,7 @@
         <v>3424.1852281459701</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>6</v>
       </c>
@@ -11364,7 +11240,7 @@
         <v>618670.85826394404</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>6</v>
       </c>
@@ -11384,7 +11260,7 @@
         <v>97332.125004328802</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>6</v>
       </c>
@@ -11404,7 +11280,7 @@
         <v>592652.73019974201</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>6</v>
       </c>
@@ -11424,7 +11300,7 @@
         <v>388691.82446322101</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>6</v>
       </c>
@@ -11444,7 +11320,7 @@
         <v>821778.828605955</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>6</v>
       </c>
@@ -11464,7 +11340,7 @@
         <v>138576.46141082601</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>6</v>
       </c>
@@ -11484,7 +11360,7 @@
         <v>2092658.9927733401</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>6</v>
       </c>
@@ -11504,7 +11380,7 @@
         <v>12243.5867614369</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>6</v>
       </c>
@@ -11524,7 +11400,7 @@
         <v>2803.3268608636299</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>6</v>
       </c>
@@ -11544,7 +11420,7 @@
         <v>709533.13878123905</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>6</v>
       </c>
@@ -11564,7 +11440,7 @@
         <v>75194.284876646096</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>6</v>
       </c>
@@ -11584,7 +11460,7 @@
         <v>763694.36076770595</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>6</v>
       </c>
@@ -11604,7 +11480,7 @@
         <v>496966.255741339</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>6</v>
       </c>
@@ -11624,7 +11500,7 @@
         <v>1223883.1118488901</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>6</v>
       </c>
@@ -11644,7 +11520,7 @@
         <v>122572.381512216</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>6</v>
       </c>
@@ -11664,7 +11540,7 @@
         <v>2414877.9861118002</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>6</v>
       </c>
@@ -11684,7 +11560,7 @@
         <v>15069.1338953467</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>6</v>
       </c>
@@ -11704,7 +11580,7 @@
         <v>3802.3508484888398</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>6</v>
       </c>
@@ -11724,7 +11600,7 @@
         <v>745700.47422865801</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>6</v>
       </c>
@@ -11744,7 +11620,7 @@
         <v>53174.741962948399</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>6</v>
       </c>
@@ -11764,7 +11640,7 @@
         <v>693380.98401164403</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>6</v>
       </c>
@@ -11784,7 +11660,7 @@
         <v>585580.29712370597</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>6</v>
       </c>
@@ -11804,7 +11680,7 @@
         <v>1734650.8556603</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>6</v>
       </c>
@@ -11824,7 +11700,7 @@
         <v>128296.242613678</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>6</v>
       </c>
@@ -11844,7 +11720,7 @@
         <v>2174364.3633635798</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>6</v>
       </c>
@@ -11864,7 +11740,7 @@
         <v>8267.0741664315701</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>6</v>
       </c>
@@ -11884,7 +11760,7 @@
         <v>4075.2369516982299</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>6</v>
       </c>
@@ -11904,7 +11780,7 @@
         <v>645081.56259865605</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>6</v>
       </c>
@@ -11924,7 +11800,7 @@
         <v>64407.6661646047</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>6</v>
       </c>
@@ -11944,7 +11820,7 @@
         <v>379914.23769169801</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>6</v>
       </c>
@@ -11964,7 +11840,7 @@
         <v>308033.13514928101</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>6</v>
       </c>
@@ -11984,7 +11860,7 @@
         <v>784189.33330312395</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>6</v>
       </c>
@@ -12004,7 +11880,7 @@
         <v>137491.74830292299</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>6</v>
       </c>
@@ -12024,7 +11900,7 @@
         <v>1415257.6210638301</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>6</v>
       </c>
@@ -12044,7 +11920,7 @@
         <v>16557.061577131401</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>6</v>
       </c>
@@ -12064,7 +11940,7 @@
         <v>2794.07510506997</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>6</v>
       </c>
@@ -12084,7 +11960,7 @@
         <v>1259557.3395161</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>6</v>
       </c>
@@ -12104,7 +11980,7 @@
         <v>123768.976103901</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>6</v>
       </c>
@@ -12124,7 +12000,7 @@
         <v>48195.512487917098</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>6</v>
       </c>
@@ -12144,7 +12020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>6</v>
       </c>
@@ -12164,7 +12040,7 @@
         <v>1329.74856781004</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>6</v>
       </c>
@@ -12184,7 +12060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>6</v>
       </c>
@@ -12204,7 +12080,7 @@
         <v>2651532.5002965699</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>6</v>
       </c>
@@ -12224,7 +12100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>6</v>
       </c>
@@ -12244,7 +12120,7 @@
         <v>5998.45878730803</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>6</v>
       </c>
@@ -12264,7 +12140,7 @@
         <v>956092.192036486</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>6</v>
       </c>
@@ -12284,7 +12160,7 @@
         <v>18217.8113474817</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>6</v>
       </c>
@@ -12304,7 +12180,7 @@
         <v>40120.265512517901</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>6</v>
       </c>
@@ -12324,7 +12200,7 @@
         <v>197.97461645569601</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>6</v>
       </c>
@@ -12344,7 +12220,7 @@
         <v>13690.638927890999</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>6</v>
       </c>
@@ -12364,7 +12240,7 @@
         <v>9618.6185412249997</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>6</v>
       </c>
@@ -12384,7 +12260,7 @@
         <v>175409.746369817</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>6</v>
       </c>
@@ -12404,7 +12280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>6</v>
       </c>
@@ -12424,7 +12300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>6</v>
       </c>
@@ -12444,7 +12320,7 @@
         <v>902007.423511039</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>6</v>
       </c>
@@ -12464,7 +12340,7 @@
         <v>39427.5971948242</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>6</v>
       </c>
@@ -12484,7 +12360,7 @@
         <v>51015.501961784401</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>6</v>
       </c>
@@ -12504,7 +12380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>6</v>
       </c>
@@ -12524,7 +12400,7 @@
         <v>10877.1808051879</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>6</v>
       </c>
@@ -12544,7 +12420,7 @@
         <v>264670.12103930902</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>6</v>
       </c>
@@ -12564,7 +12440,7 @@
         <v>346248.81834444503</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>6</v>
       </c>
@@ -12584,7 +12460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>6</v>
       </c>
@@ -12604,7 +12480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>6</v>
       </c>
@@ -12624,7 +12500,7 @@
         <v>2267221.99672485</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>6</v>
       </c>
@@ -12644,7 +12520,7 @@
         <v>45231.263001686697</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>6</v>
       </c>
@@ -12664,7 +12540,7 @@
         <v>136207.55558523099</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>6</v>
       </c>
@@ -12684,7 +12560,7 @@
         <v>428.51767034247001</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>6</v>
       </c>
@@ -12704,7 +12580,7 @@
         <v>5517.1907293163604</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>6</v>
       </c>
@@ -12724,7 +12600,7 @@
         <v>2225.7892632445601</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>6</v>
       </c>
@@ -12744,7 +12620,7 @@
         <v>1987096.1031390999</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>6</v>
       </c>
@@ -12764,7 +12640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>6</v>
       </c>
@@ -12784,7 +12660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>6</v>
       </c>
@@ -12804,7 +12680,7 @@
         <v>539125.55350419902</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>6</v>
       </c>
@@ -12824,7 +12700,7 @@
         <v>3386.3955464978299</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>6</v>
       </c>
@@ -12844,7 +12720,7 @@
         <v>90995.612445205697</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>6</v>
       </c>
@@ -12864,7 +12740,7 @@
         <v>1278.9268446000001</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>6</v>
       </c>
@@ -12884,7 +12760,7 @@
         <v>8438.1246783543102</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>6</v>
       </c>
@@ -12904,7 +12780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>6</v>
       </c>
@@ -12924,7 +12800,7 @@
         <v>232679.43824531601</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>6</v>
       </c>
@@ -12944,7 +12820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>6</v>
       </c>
@@ -12964,7 +12840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>6</v>
       </c>
@@ -12984,7 +12860,7 @@
         <v>2135628.6918428498</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>6</v>
       </c>
@@ -13004,7 +12880,7 @@
         <v>7032.9327590491803</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>6</v>
       </c>
@@ -13024,7 +12900,7 @@
         <v>48378.326887514697</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>6</v>
       </c>
@@ -13044,7 +12920,7 @@
         <v>46676.153596282202</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>6</v>
       </c>
@@ -13064,7 +12940,7 @@
         <v>25041.103835003199</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>6</v>
       </c>
@@ -13084,7 +12960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>6</v>
       </c>
@@ -13104,7 +12980,7 @@
         <v>748557.15458479</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>6</v>
       </c>
@@ -13124,7 +13000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>6</v>
       </c>
@@ -13144,7 +13020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>6</v>
       </c>
@@ -13164,7 +13040,7 @@
         <v>356922.95806078298</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>6</v>
       </c>
@@ -13184,7 +13060,7 @@
         <v>202263.24784085201</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>6</v>
       </c>
@@ -13204,7 +13080,7 @@
         <v>174535.27302290199</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>6</v>
       </c>
@@ -13224,7 +13100,7 @@
         <v>7511.74275757956</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>6</v>
       </c>
@@ -13244,7 +13120,7 @@
         <v>304017.89020798402</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>6</v>
       </c>
@@ -13264,7 +13140,7 @@
         <v>373.69691930174099</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>6</v>
       </c>
@@ -13284,7 +13160,7 @@
         <v>965210.16438214795</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>6</v>
       </c>
@@ -13304,7 +13180,7 @@
         <v>34314.051172684798</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>6</v>
       </c>
@@ -13324,7 +13200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>6</v>
       </c>
@@ -13344,7 +13220,7 @@
         <v>11400405.1913424</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>6</v>
       </c>
@@ -13364,7 +13240,7 @@
         <v>1120247.91046423</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>6</v>
       </c>
@@ -13384,7 +13260,7 @@
         <v>436223.38858986698</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>6</v>
       </c>
@@ -13404,7 +13280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>6</v>
       </c>
@@ -13424,7 +13300,7 @@
         <v>12035.714453042499</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>6</v>
       </c>
@@ -13444,7 +13320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>6</v>
       </c>
@@ -13464,7 +13340,7 @@
         <v>23999340.032450501</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>6</v>
       </c>
@@ -13484,7 +13360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>6</v>
       </c>
@@ -13504,7 +13380,7 @@
         <v>54292.772987364697</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>6</v>
       </c>
@@ -13524,7 +13400,7 @@
         <v>8653705.5896859504</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>6</v>
       </c>
@@ -13544,7 +13420,7 @@
         <v>164891.604808264</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>6</v>
       </c>
@@ -13564,7 +13440,7 @@
         <v>363133.35556673398</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>6</v>
       </c>
@@ -13584,7 +13460,7 @@
         <v>1791.8920992226001</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>6</v>
       </c>
@@ -13604,7 +13480,7 @@
         <v>123915.621948873</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>6</v>
       </c>
@@ -13624,7 +13500,7 @@
         <v>87059.274961717907</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>6</v>
       </c>
@@ -13644,7 +13520,7 @@
         <v>1587654.74217779</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>6</v>
       </c>
@@ -13664,7 +13540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>6</v>
       </c>
@@ -13684,7 +13560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>6</v>
       </c>
@@ -13704,7 +13580,7 @@
         <v>8164177.8353502201</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>6</v>
       </c>
@@ -13724,7 +13600,7 @@
         <v>356863.93119265098</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>6</v>
       </c>
@@ -13744,7 +13620,7 @@
         <v>461747.45298043598</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>6</v>
       </c>
@@ -13764,7 +13640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>6</v>
       </c>
@@ -13784,7 +13660,7 @@
         <v>98450.673604379001</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>6</v>
       </c>
@@ -13804,7 +13680,7 @@
         <v>2395561.1445609899</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>6</v>
       </c>
@@ -13824,7 +13700,7 @@
         <v>3133939.7598753301</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>6</v>
       </c>
@@ -13844,7 +13720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>6</v>
       </c>
@@ -13864,7 +13740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>6</v>
       </c>
@@ -13884,7 +13760,7 @@
         <v>20520899.375118699</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>6</v>
       </c>
@@ -13904,7 +13780,7 @@
         <v>409393.609451539</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>6</v>
       </c>
@@ -13924,7 +13800,7 @@
         <v>1232830.9915539999</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>6</v>
       </c>
@@ -13944,7 +13820,7 @@
         <v>3878.5650484428702</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>6</v>
       </c>
@@ -13964,7 +13840,7 @@
         <v>49936.7578266204</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>6</v>
       </c>
@@ -13984,7 +13860,7 @@
         <v>20145.886713890799</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>6</v>
       </c>
@@ -14004,7 +13880,7 @@
         <v>17985446.171619698</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>6</v>
       </c>
@@ -14024,7 +13900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>6</v>
       </c>
@@ -14044,7 +13920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>6</v>
       </c>
@@ -14064,7 +13940,7 @@
         <v>4879690.3214578303</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>6</v>
       </c>
@@ -14084,7 +13960,7 @@
         <v>30650.673976529601</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>6</v>
       </c>
@@ -14104,7 +13980,7 @@
         <v>823612.24849739496</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>6</v>
       </c>
@@ -14124,7 +14000,7 @@
         <v>11575.7209148845</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>6</v>
       </c>
@@ -14144,7 +14020,7 @@
         <v>76374.482820538993</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>6</v>
       </c>
@@ -14164,7 +14040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>6</v>
       </c>
@@ -14184,7 +14060,7 @@
         <v>2106009.6213703598</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>6</v>
       </c>
@@ -14204,7 +14080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>6</v>
       </c>
@@ -14224,7 +14100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>6</v>
       </c>
@@ -14244,7 +14120,7 @@
         <v>19329832.5224571</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>6</v>
       </c>
@@ -14264,7 +14140,7 @@
         <v>63655.921506099803</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>6</v>
       </c>
@@ -14284,7 +14160,7 @@
         <v>437878.063740285</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>6</v>
       </c>
@@ -14304,7 +14180,7 @@
         <v>422471.48825766699</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>6</v>
       </c>
@@ -14324,7 +14200,7 @@
         <v>226650.04696597799</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>6</v>
       </c>
@@ -14344,7 +14220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>6</v>
       </c>
@@ -14364,7 +14240,7 @@
         <v>6775280.96849328</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>6</v>
       </c>
@@ -14384,7 +14260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>6</v>
       </c>
@@ -14404,7 +14280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>6</v>
       </c>
@@ -14424,7 +14300,7 @@
         <v>3230552.6841285098</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>6</v>
       </c>
@@ -14444,7 +14320,7 @@
         <v>1830709.0184474799</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>6</v>
       </c>
@@ -14464,7 +14340,7 @@
         <v>1579739.7785871101</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>6</v>
       </c>
@@ -14484,7 +14360,7 @@
         <v>67989.688474590803</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>6</v>
       </c>
@@ -14504,7 +14380,7 @@
         <v>2751702.5426738001</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>6</v>
       </c>
@@ -14524,7 +14400,7 @@
         <v>3382.3758277135898</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>6</v>
       </c>
@@ -14544,7 +14420,7 @@
         <v>8736233.4556302298</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>6</v>
       </c>
@@ -14564,7 +14440,7 @@
         <v>310580.61022895802</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>6</v>
       </c>
@@ -14584,7 +14460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>6</v>
       </c>
@@ -14604,7 +14480,7 @@
         <v>350612.074550113</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>6</v>
       </c>
@@ -14624,7 +14500,7 @@
         <v>34452.498600350104</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>6</v>
       </c>
@@ -14644,7 +14520,7 @@
         <v>13415.767656825699</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>6</v>
       </c>
@@ -14664,7 +14540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>6</v>
       </c>
@@ -14684,7 +14560,7 @@
         <v>370.15059923283599</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>6</v>
       </c>
@@ -14704,7 +14580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>6</v>
       </c>
@@ -14724,7 +14600,7 @@
         <v>738084.15186821995</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>6</v>
       </c>
@@ -14744,7 +14620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>6</v>
       </c>
@@ -14764,7 +14640,7 @@
         <v>1669.7390531897399</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>6</v>
       </c>
@@ -14784,7 +14660,7 @@
         <v>266139.10807738302</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>6</v>
       </c>
@@ -14804,7 +14680,7 @@
         <v>5071.1344612212797</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>6</v>
       </c>
@@ -14824,7 +14700,7 @@
         <v>11167.9310512786</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>6</v>
       </c>
@@ -14844,7 +14720,7 @@
         <v>55.108480420965797</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>6</v>
       </c>
@@ -14864,7 +14740,7 @@
         <v>3810.9446595495001</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>6</v>
       </c>
@@ -14884,7 +14760,7 @@
         <v>2677.4515897317501</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>6</v>
       </c>
@@ -14904,7 +14780,7 @@
         <v>48827.292844539399</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>6</v>
       </c>
@@ -14924,7 +14800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>6</v>
       </c>
@@ -14944,7 +14820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>6</v>
       </c>
@@ -14964,7 +14840,7 @@
         <v>251083.999191621</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>6</v>
       </c>
@@ -14984,7 +14860,7 @@
         <v>10975.118967046699</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>6</v>
       </c>
@@ -15004,7 +14880,7 @@
         <v>14200.7437183538</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>6</v>
       </c>
@@ -15024,7 +14900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>6</v>
       </c>
@@ -15044,7 +14920,7 @@
         <v>3027.7866737130098</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>6</v>
       </c>
@@ -15064,7 +14940,7 @@
         <v>73673.930751489097</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>6</v>
       </c>
@@ -15084,7 +14960,7 @@
         <v>96382.286618989499</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>6</v>
       </c>
@@ -15104,7 +14980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>6</v>
       </c>
@@ -15124,7 +15000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>6</v>
       </c>
@@ -15144,7 +15020,7 @@
         <v>631106.96337405394</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>6</v>
       </c>
@@ -15164,7 +15040,7 @@
         <v>12590.635184293</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>6</v>
       </c>
@@ -15184,7 +15060,7 @@
         <v>37914.918308913999</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>6</v>
       </c>
@@ -15204,7 +15080,7 @@
         <v>119.282754874742</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>6</v>
       </c>
@@ -15224,7 +15100,7 @@
         <v>1535.77262948407</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>6</v>
       </c>
@@ -15244,7 +15120,7 @@
         <v>619.57369197459104</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>6</v>
       </c>
@@ -15264,7 +15140,7 @@
         <v>553130.74299569195</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>6</v>
       </c>
@@ -15284,7 +15160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>6</v>
       </c>
@@ -15304,7 +15180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>6</v>
       </c>
@@ -15324,7 +15200,7 @@
         <v>150071.71394812301</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>6</v>
       </c>
@@ -15344,7 +15220,7 @@
         <v>942.64161745999797</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>6</v>
       </c>
@@ -15364,7 +15240,7 @@
         <v>25329.661027289399</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>6</v>
       </c>
@@ -15384,7 +15260,7 @@
         <v>356.00379602836199</v>
       </c>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>6</v>
       </c>
@@ -15404,7 +15280,7 @@
         <v>2348.8477308444299</v>
       </c>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>6</v>
       </c>
@@ -15424,7 +15300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>6</v>
       </c>
@@ -15444,7 +15320,7 @@
         <v>64768.961276186797</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>6</v>
       </c>
@@ -15464,7 +15340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>6</v>
       </c>
@@ -15484,7 +15360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>6</v>
       </c>
@@ -15504,7 +15380,7 @@
         <v>594476.47409489797</v>
       </c>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>6</v>
       </c>
@@ -15524,7 +15400,7 @@
         <v>1957.69661885297</v>
       </c>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>6</v>
       </c>
@@ -15544,7 +15420,7 @@
         <v>13466.6561188985</v>
       </c>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>6</v>
       </c>
@@ -15564,7 +15440,7 @@
         <v>12992.836872914801</v>
       </c>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>6</v>
       </c>
@@ -15584,7 +15460,7 @@
         <v>6970.4753322225397</v>
       </c>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>6</v>
       </c>
@@ -15604,7 +15480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>6</v>
       </c>
@@ -15624,7 +15500,7 @@
         <v>208369.376013623</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>6</v>
       </c>
@@ -15644,7 +15520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>6</v>
       </c>
@@ -15664,7 +15540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>6</v>
       </c>
@@ -15684,7 +15560,7 @@
         <v>99353.554502211002</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>6</v>
       </c>
@@ -15704,7 +15580,7 @@
         <v>56302.269619564999</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>6</v>
       </c>
@@ -15724,7 +15600,7 @@
         <v>48583.873267929601</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>6</v>
       </c>
@@ -15744,7 +15620,7 @@
         <v>2090.9788138220401</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>6</v>
       </c>
@@ -15764,7 +15640,7 @@
         <v>84626.828681819898</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>6</v>
       </c>
@@ -15784,7 +15660,7 @@
         <v>104.022776906472</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>6</v>
       </c>
@@ -15804,7 +15680,7 @@
         <v>268677.19911940902</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>6</v>
       </c>
@@ -15824,7 +15700,7 @@
         <v>9551.70542096797</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>6</v>
       </c>
@@ -15844,7 +15720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>6</v>
       </c>
@@ -15864,7 +15740,7 @@
         <v>3342250.68483405</v>
       </c>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>6</v>
       </c>
@@ -15884,7 +15760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>6</v>
       </c>
@@ -15904,7 +15780,7 @@
         <v>1649569.6413877499</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>6</v>
       </c>
@@ -15924,7 +15800,7 @@
         <v>80078.671339680004</v>
       </c>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>6</v>
       </c>
@@ -15944,7 +15820,7 @@
         <v>646639.800743122</v>
       </c>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>6</v>
       </c>
@@ -15964,7 +15840,7 @@
         <v>214207.25313839901</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>6</v>
       </c>
@@ -15984,7 +15860,7 @@
         <v>1201159.3831584801</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>6</v>
       </c>
@@ -16004,7 +15880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>6</v>
       </c>
@@ -16024,7 +15900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>6</v>
       </c>
@@ -16044,7 +15920,7 @@
         <v>1791903.9219628801</v>
       </c>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>6</v>
       </c>
@@ -16064,7 +15940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>6</v>
       </c>
@@ -16084,7 +15960,7 @@
         <v>257800.54361533801</v>
       </c>
     </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>6</v>
       </c>
@@ -16104,7 +15980,7 @@
         <v>44576.827522996296</v>
       </c>
     </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>6</v>
       </c>
@@ -16124,7 +16000,7 @@
         <v>215791.23084662799</v>
       </c>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>6</v>
       </c>
@@ -16144,7 +16020,7 @@
         <v>126145.792384463</v>
       </c>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>6</v>
       </c>
@@ -16164,7 +16040,7 @@
         <v>2553139.0927953599</v>
       </c>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>6</v>
       </c>
@@ -16184,7 +16060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>6</v>
       </c>
@@ -16204,7 +16080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>6</v>
       </c>
@@ -16224,7 +16100,7 @@
         <v>4552420.7137126997</v>
       </c>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>6</v>
       </c>
@@ -16244,7 +16120,7 @@
         <v>22053.6829484466</v>
       </c>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>6</v>
       </c>
@@ -16264,7 +16140,7 @@
         <v>472795.45743923303</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>6</v>
       </c>
@@ -16284,7 +16160,7 @@
         <v>1164942.8761245899</v>
       </c>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>6</v>
       </c>
@@ -16304,7 +16180,7 @@
         <v>3450410.6621809402</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>6</v>
       </c>
@@ -16324,7 +16200,7 @@
         <v>290275.62876363302</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>6</v>
       </c>
@@ -16344,7 +16220,7 @@
         <v>7711723.9638985097</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>6</v>
       </c>
@@ -16364,7 +16240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>6</v>
       </c>
@@ -16384,7 +16260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>6</v>
       </c>
@@ -16404,7 +16280,7 @@
         <v>7976737.0349562904</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>6</v>
       </c>
@@ -16424,7 +16300,7 @@
         <v>14514.531868419101</v>
       </c>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>6</v>
       </c>
@@ -16444,7 +16320,7 @@
         <v>1220296.3154463</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>6</v>
       </c>
@@ -16464,7 +16340,7 @@
         <v>1512867.0803916601</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>6</v>
       </c>
@@ -16484,7 +16360,7 @@
         <v>2227803.3477135198</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>6</v>
       </c>
@@ -16504,7 +16380,7 @@
         <v>341655.75545258803</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>6</v>
       </c>
@@ -16524,7 +16400,7 @@
         <v>7485153.0920584397</v>
       </c>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>6</v>
       </c>
@@ -16544,7 +16420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>6</v>
       </c>
@@ -16564,7 +16440,7 @@
         <v>27488.995455730099</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>6</v>
       </c>
@@ -16584,7 +16460,7 @@
         <v>12225708.034163101</v>
       </c>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>6</v>
       </c>
@@ -16604,7 +16480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>6</v>
       </c>
@@ -16624,7 +16500,7 @@
         <v>2234696.5768270101</v>
       </c>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>6</v>
       </c>
@@ -16644,7 +16520,7 @@
         <v>1917341.26135732</v>
       </c>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>6</v>
       </c>
@@ -16664,7 +16540,7 @@
         <v>3762039.61067309</v>
       </c>
     </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>6</v>
       </c>
@@ -16684,7 +16560,7 @@
         <v>46606.480368479999</v>
       </c>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>6</v>
       </c>
@@ -16704,7 +16580,7 @@
         <v>9238377.9294521697</v>
       </c>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>6</v>
       </c>
@@ -16724,7 +16600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>6</v>
       </c>
@@ -16744,7 +16620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>6</v>
       </c>
@@ -16764,7 +16640,7 @@
         <v>10285188.831037</v>
       </c>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>6</v>
       </c>
@@ -16784,7 +16660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>6</v>
       </c>
@@ -16804,7 +16680,7 @@
         <v>1112209.8917967801</v>
       </c>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>6</v>
       </c>
@@ -16824,7 +16700,7 @@
         <v>3233940.8815252101</v>
       </c>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>6</v>
       </c>
@@ -16844,7 +16720,7 @@
         <v>3219370.4892361499</v>
       </c>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>6</v>
       </c>
@@ -16864,7 +16740,7 @@
         <v>40446.950965930999</v>
       </c>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>6</v>
       </c>
@@ -16884,7 +16760,7 @@
         <v>7653125.7990597803</v>
       </c>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>6</v>
       </c>
@@ -16904,7 +16780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>6</v>
       </c>
@@ -16924,7 +16800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>6</v>
       </c>
@@ -16944,7 +16820,7 @@
         <v>9540042.3299236298</v>
       </c>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>6</v>
       </c>
@@ -16964,7 +16840,7 @@
         <v>25867.1089215869</v>
       </c>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>6</v>
       </c>
@@ -16984,7 +16860,7 @@
         <v>1518073.79666619</v>
       </c>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>6</v>
       </c>
@@ -17004,7 +16880,7 @@
         <v>747122.54636573396</v>
       </c>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>6</v>
       </c>
@@ -17024,7 +16900,7 @@
         <v>3267493.5124234101</v>
       </c>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>6</v>
       </c>
@@ -17044,7 +16920,7 @@
         <v>325862.13571958302</v>
       </c>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>6</v>
       </c>
@@ -17064,7 +16940,7 @@
         <v>10205016.023724601</v>
       </c>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>6</v>
       </c>
@@ -17084,7 +16960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>6</v>
       </c>
@@ -17104,7 +16980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>22</v>
       </c>
@@ -17124,7 +17000,7 @@
         <v>2062894.6183366701</v>
       </c>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>22</v>
       </c>
@@ -17144,7 +17020,7 @@
         <v>7354933.3304143399</v>
       </c>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>22</v>
       </c>
@@ -17164,7 +17040,7 @@
         <v>1414828.08856885</v>
       </c>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>22</v>
       </c>
@@ -17184,7 +17060,7 @@
         <v>830338.76272469899</v>
       </c>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>22</v>
       </c>
@@ -17204,7 +17080,7 @@
         <v>1706512.63212364</v>
       </c>
     </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>22</v>
       </c>
@@ -17224,7 +17100,7 @@
         <v>632975.70226676005</v>
       </c>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>22</v>
       </c>
@@ -17244,7 +17120,7 @@
         <v>801232.25475347997</v>
       </c>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>22</v>
       </c>
@@ -17264,7 +17140,7 @@
         <v>11871056.360396599</v>
       </c>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>22</v>
       </c>
@@ -17284,7 +17160,7 @@
         <v>1280281.7702413399</v>
       </c>
     </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>22</v>
       </c>
@@ -17304,7 +17180,7 @@
         <v>2754128.7310842299</v>
       </c>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>22</v>
       </c>
@@ -17324,7 +17200,7 @@
         <v>5987646.9007378304</v>
       </c>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>22</v>
       </c>
@@ -17344,7 +17220,7 @@
         <v>1201973.8714914201</v>
       </c>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>22</v>
       </c>
@@ -17364,7 +17240,7 @@
         <v>1589480.53464974</v>
       </c>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>22</v>
       </c>
@@ -17384,7 +17260,7 @@
         <v>1851359.9606798</v>
       </c>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>22</v>
       </c>
@@ -17404,7 +17280,7 @@
         <v>312909.68580755201</v>
       </c>
     </row>
-    <row r="458" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>22</v>
       </c>
@@ -17424,7 +17300,7 @@
         <v>458954.84428603202</v>
       </c>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>22</v>
       </c>
@@ -17444,7 +17320,7 @@
         <v>9120104.5267663207</v>
       </c>
     </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>22</v>
       </c>
@@ -17464,7 +17340,7 @@
         <v>1474636.2622038401</v>
       </c>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>22</v>
       </c>
@@ -17484,7 +17360,7 @@
         <v>2432319.7555669299</v>
       </c>
     </row>
-    <row r="462" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>22</v>
       </c>
@@ -17504,7 +17380,7 @@
         <v>5388821.6427429402</v>
       </c>
     </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>22</v>
       </c>
@@ -17524,7 +17400,7 @@
         <v>939480.47566590097</v>
       </c>
     </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>22</v>
       </c>
@@ -17544,7 +17420,7 @@
         <v>685248.57533590996</v>
       </c>
     </row>
-    <row r="465" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>22</v>
       </c>
@@ -17564,7 +17440,7 @@
         <v>1354391.46980905</v>
       </c>
     </row>
-    <row r="466" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>22</v>
       </c>
@@ -17584,7 +17460,7 @@
         <v>220567.270910352</v>
       </c>
     </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>22</v>
       </c>
@@ -17604,7 +17480,7 @@
         <v>191481.374440443</v>
       </c>
     </row>
-    <row r="468" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>22</v>
       </c>
@@ -17624,7 +17500,7 @@
         <v>10396147.9941236</v>
       </c>
     </row>
-    <row r="469" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>22</v>
       </c>
@@ -17644,7 +17520,7 @@
         <v>1855960.7204346801</v>
       </c>
     </row>
-    <row r="470" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>22</v>
       </c>
@@ -17664,7 +17540,7 @@
         <v>2530297.1740174498</v>
       </c>
     </row>
-    <row r="471" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>22</v>
       </c>
@@ -17684,7 +17560,7 @@
         <v>6383328.7905182596</v>
       </c>
     </row>
-    <row r="472" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>22</v>
       </c>
@@ -17704,7 +17580,7 @@
         <v>1447698.3454084699</v>
       </c>
     </row>
-    <row r="473" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>22</v>
       </c>
@@ -17724,7 +17600,7 @@
         <v>1234783.06335603</v>
       </c>
     </row>
-    <row r="474" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>22</v>
       </c>
@@ -17744,7 +17620,7 @@
         <v>1845416.58179543</v>
       </c>
     </row>
-    <row r="475" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>22</v>
       </c>
@@ -17764,7 +17640,7 @@
         <v>193257.108427061</v>
       </c>
     </row>
-    <row r="476" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>22</v>
       </c>
@@ -17784,7 +17660,7 @@
         <v>492757.70058021997</v>
       </c>
     </row>
-    <row r="477" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>22</v>
       </c>
@@ -17804,7 +17680,7 @@
         <v>11404271.4873221</v>
       </c>
     </row>
-    <row r="478" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>22</v>
       </c>
@@ -17824,7 +17700,7 @@
         <v>2243878.9053749698</v>
       </c>
     </row>
-    <row r="479" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>22</v>
       </c>
@@ -17844,7 +17720,7 @@
         <v>1822608.5383377499</v>
       </c>
     </row>
-    <row r="480" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>22</v>
       </c>
@@ -17864,7 +17740,7 @@
         <v>5269355.4624828398</v>
       </c>
     </row>
-    <row r="481" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>22</v>
       </c>
@@ -17884,7 +17760,7 @@
         <v>1424237.52915785</v>
       </c>
     </row>
-    <row r="482" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>22</v>
       </c>
@@ -17904,7 +17780,7 @@
         <v>1067223.6671384801</v>
       </c>
     </row>
-    <row r="483" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>22</v>
       </c>
@@ -17924,7 +17800,7 @@
         <v>1829168.0993513099</v>
       </c>
     </row>
-    <row r="484" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>22</v>
       </c>
@@ -17944,7 +17820,7 @@
         <v>164360.427310286</v>
       </c>
     </row>
-    <row r="485" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>22</v>
       </c>
@@ -17964,7 +17840,7 @@
         <v>138995.86961288299</v>
       </c>
     </row>
-    <row r="486" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>22</v>
       </c>
@@ -17984,7 +17860,7 @@
         <v>10975053.858083</v>
       </c>
     </row>
-    <row r="487" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>22</v>
       </c>
@@ -18004,7 +17880,7 @@
         <v>1903390.9758756901</v>
       </c>
     </row>
-    <row r="488" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>22</v>
       </c>
@@ -18024,7 +17900,7 @@
         <v>2718731.0114158499</v>
       </c>
     </row>
-    <row r="489" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
         <v>22</v>
       </c>
@@ -18044,7 +17920,7 @@
         <v>7265336.1234959997</v>
       </c>
     </row>
-    <row r="490" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
         <v>22</v>
       </c>
@@ -18064,7 +17940,7 @@
         <v>950821.95357171597</v>
       </c>
     </row>
-    <row r="491" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
         <v>22</v>
       </c>
@@ -18084,7 +17960,7 @@
         <v>1128299.1564812299</v>
       </c>
     </row>
-    <row r="492" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
         <v>22</v>
       </c>
@@ -18104,7 +17980,7 @@
         <v>2145658.1481381501</v>
       </c>
     </row>
-    <row r="493" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
         <v>22</v>
       </c>
@@ -18124,7 +18000,7 @@
         <v>199964.31804141501</v>
       </c>
     </row>
-    <row r="494" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
         <v>22</v>
       </c>
@@ -18144,7 +18020,7 @@
         <v>305335.93633128202</v>
       </c>
     </row>
-    <row r="495" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
         <v>22</v>
       </c>
@@ -18164,7 +18040,7 @@
         <v>15892114.940760801</v>
       </c>
     </row>
-    <row r="496" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
         <v>22</v>
       </c>
@@ -18184,7 +18060,7 @@
         <v>2232286.8020333699</v>
       </c>
     </row>
-    <row r="497" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
         <v>22</v>
       </c>
@@ -18204,7 +18080,7 @@
         <v>5899990.5214380696</v>
       </c>
     </row>
-    <row r="498" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
         <v>22</v>
       </c>
@@ -18224,7 +18100,7 @@
         <v>6763891.2931651603</v>
       </c>
     </row>
-    <row r="499" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
         <v>22</v>
       </c>
@@ -18244,7 +18120,7 @@
         <v>1263921.69145297</v>
       </c>
     </row>
-    <row r="500" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
         <v>22</v>
       </c>
@@ -18264,7 +18140,7 @@
         <v>1995252.9831205299</v>
       </c>
     </row>
-    <row r="501" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
         <v>22</v>
       </c>
@@ -18284,7 +18160,7 @@
         <v>2807416.38881785</v>
       </c>
     </row>
-    <row r="502" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
         <v>22</v>
       </c>
@@ -18304,7 +18180,7 @@
         <v>314714.95926892699</v>
       </c>
     </row>
-    <row r="503" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
         <v>22</v>
       </c>
@@ -18324,7 +18200,7 @@
         <v>619496.68861215701</v>
       </c>
     </row>
-    <row r="504" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
         <v>22</v>
       </c>
@@ -18344,7 +18220,7 @@
         <v>18194822.348613501</v>
       </c>
     </row>
-    <row r="505" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
         <v>22</v>
       </c>
@@ -18364,7 +18240,7 @@
         <v>2380925.4700070499</v>
       </c>
     </row>
-    <row r="506" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
         <v>32</v>
       </c>
@@ -18384,7 +18260,7 @@
         <v>183724.18996678799</v>
       </c>
     </row>
-    <row r="507" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
         <v>32</v>
       </c>
@@ -18404,7 +18280,7 @@
         <v>421224.116588148</v>
       </c>
     </row>
-    <row r="508" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
         <v>32</v>
       </c>
@@ -18424,7 +18300,7 @@
         <v>249871.99233432399</v>
       </c>
     </row>
-    <row r="509" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
         <v>32</v>
       </c>
@@ -18444,7 +18320,7 @@
         <v>395.48879124553901</v>
       </c>
     </row>
-    <row r="510" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
         <v>32</v>
       </c>
@@ -18464,7 +18340,7 @@
         <v>568444.70490103203</v>
       </c>
     </row>
-    <row r="511" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
         <v>32</v>
       </c>
@@ -18484,7 +18360,7 @@
         <v>168961.73120133599</v>
       </c>
     </row>
-    <row r="512" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
         <v>32</v>
       </c>
@@ -18504,7 +18380,7 @@
         <v>182391.01808420999</v>
       </c>
     </row>
-    <row r="513" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
         <v>32</v>
       </c>
@@ -18524,7 +18400,7 @@
         <v>1239.20375209995</v>
       </c>
     </row>
-    <row r="514" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
         <v>32</v>
       </c>
@@ -18544,7 +18420,7 @@
         <v>712.39110748761004</v>
       </c>
     </row>
-    <row r="515" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
         <v>32</v>
       </c>
@@ -18564,7 +18440,7 @@
         <v>423308.97921550699</v>
       </c>
     </row>
-    <row r="516" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
         <v>32</v>
       </c>
@@ -18584,7 +18460,7 @@
         <v>134853.92453732999</v>
       </c>
     </row>
-    <row r="517" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
         <v>32</v>
       </c>
@@ -18604,7 +18480,7 @@
         <v>1321.70829477045</v>
       </c>
     </row>
-    <row r="518" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
         <v>32</v>
       </c>
@@ -18624,7 +18500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="519" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
         <v>32</v>
       </c>
@@ -18644,7 +18520,7 @@
         <v>212612.53706642499</v>
       </c>
     </row>
-    <row r="520" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
         <v>32</v>
       </c>
@@ -18664,7 +18540,7 @@
         <v>344523.03160341398</v>
       </c>
     </row>
-    <row r="521" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
         <v>32</v>
       </c>
@@ -18684,7 +18560,7 @@
         <v>213650.43461693201</v>
       </c>
     </row>
-    <row r="522" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
         <v>32</v>
       </c>
@@ -18704,7 +18580,7 @@
         <v>921.27453269547902</v>
       </c>
     </row>
-    <row r="523" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
         <v>32</v>
       </c>
@@ -18724,7 +18600,7 @@
         <v>612782.94878547895</v>
       </c>
     </row>
-    <row r="524" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
         <v>32</v>
       </c>
@@ -18744,7 +18620,7 @@
         <v>346094.90773749998</v>
       </c>
     </row>
-    <row r="525" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
         <v>32</v>
       </c>
@@ -18764,7 +18640,7 @@
         <v>142612.25063607699</v>
       </c>
     </row>
-    <row r="526" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
         <v>32</v>
       </c>
@@ -18784,7 +18660,7 @@
         <v>5766.1690370561801</v>
       </c>
     </row>
-    <row r="527" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
         <v>32</v>
       </c>
@@ -18804,7 +18680,7 @@
         <v>7152.44937765137</v>
       </c>
     </row>
-    <row r="528" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
         <v>32</v>
       </c>
@@ -18824,7 +18700,7 @@
         <v>362681.78253373998</v>
       </c>
     </row>
-    <row r="529" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
         <v>32</v>
       </c>
@@ -18844,7 +18720,7 @@
         <v>124609.07497892401</v>
       </c>
     </row>
-    <row r="530" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
         <v>32</v>
       </c>
@@ -18864,7 +18740,7 @@
         <v>4055.1457880191601</v>
       </c>
     </row>
-    <row r="531" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
         <v>32</v>
       </c>
@@ -18884,7 +18760,7 @@
         <v>107.67228347324701</v>
       </c>
     </row>
-    <row r="532" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
         <v>32</v>
       </c>
@@ -18904,7 +18780,7 @@
         <v>196099.052564802</v>
       </c>
     </row>
-    <row r="533" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
         <v>32</v>
       </c>
@@ -18924,7 +18800,7 @@
         <v>269076.479197849</v>
       </c>
     </row>
-    <row r="534" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
         <v>32</v>
       </c>
@@ -18944,7 +18820,7 @@
         <v>179141.14290896701</v>
       </c>
     </row>
-    <row r="535" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
         <v>32</v>
       </c>
@@ -18964,7 +18840,7 @@
         <v>396.17967563048001</v>
       </c>
     </row>
-    <row r="536" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
         <v>32</v>
       </c>
@@ -18984,7 +18860,7 @@
         <v>528516.86256556294</v>
       </c>
     </row>
-    <row r="537" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
         <v>32</v>
       </c>
@@ -19004,7 +18880,7 @@
         <v>131950.66525964899</v>
       </c>
     </row>
-    <row r="538" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
         <v>32</v>
       </c>
@@ -19024,7 +18900,7 @@
         <v>204113.692075331</v>
       </c>
     </row>
-    <row r="539" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
         <v>32</v>
       </c>
@@ -19044,7 +18920,7 @@
         <v>6603.6497186615898</v>
       </c>
     </row>
-    <row r="540" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
         <v>32</v>
       </c>
@@ -19064,7 +18940,7 @@
         <v>2200.75134174717</v>
       </c>
     </row>
-    <row r="541" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
         <v>32</v>
       </c>
@@ -19084,7 +18960,7 @@
         <v>357179.878214614</v>
       </c>
     </row>
-    <row r="542" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
         <v>32</v>
       </c>
@@ -19104,7 +18980,7 @@
         <v>115767.21365451301</v>
       </c>
     </row>
-    <row r="543" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
         <v>32</v>
       </c>
@@ -19124,7 +19000,7 @@
         <v>2561.0361496312098</v>
       </c>
     </row>
-    <row r="544" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
         <v>32</v>
       </c>
@@ -19144,7 +19020,7 @@
         <v>7.9887817672362402</v>
       </c>
     </row>
-    <row r="545" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
         <v>32</v>
       </c>
@@ -19164,7 +19040,7 @@
         <v>222550.18142068401</v>
       </c>
     </row>
-    <row r="546" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
         <v>32</v>
       </c>
@@ -19184,7 +19060,7 @@
         <v>245799.58191511201</v>
       </c>
     </row>
-    <row r="547" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
         <v>32</v>
       </c>
@@ -19204,7 +19080,7 @@
         <v>205341.607597113</v>
       </c>
     </row>
-    <row r="548" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
         <v>32</v>
       </c>
@@ -19224,7 +19100,7 @@
         <v>563.07545696374405</v>
       </c>
     </row>
-    <row r="549" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
         <v>32</v>
       </c>
@@ -19244,7 +19120,7 @@
         <v>665950.62694669096</v>
       </c>
     </row>
-    <row r="550" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
         <v>32</v>
       </c>
@@ -19264,7 +19140,7 @@
         <v>381225.17406209302</v>
       </c>
     </row>
-    <row r="551" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
         <v>32</v>
       </c>
@@ -19284,7 +19160,7 @@
         <v>209705.183452795</v>
       </c>
     </row>
-    <row r="552" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
         <v>32</v>
       </c>
@@ -19304,7 +19180,7 @@
         <v>5707.2562612414704</v>
       </c>
     </row>
-    <row r="553" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
         <v>32</v>
       </c>
@@ -19324,7 +19200,7 @@
         <v>11582.057924173499</v>
       </c>
     </row>
-    <row r="554" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
         <v>32</v>
       </c>
@@ -19344,7 +19220,7 @@
         <v>363625.15954229998</v>
       </c>
     </row>
-    <row r="555" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
         <v>32</v>
       </c>
@@ -19364,7 +19240,7 @@
         <v>149417.89600476099</v>
       </c>
     </row>
-    <row r="556" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
         <v>32</v>
       </c>
@@ -19384,7 +19260,7 @@
         <v>3417.3963678570699</v>
       </c>
     </row>
-    <row r="557" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
         <v>32</v>
       </c>
@@ -19404,7 +19280,7 @@
         <v>39.945332932959602</v>
       </c>
     </row>
-    <row r="558" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
         <v>32</v>
       </c>
@@ -19424,7 +19300,7 @@
         <v>211331.71433573001</v>
       </c>
     </row>
-    <row r="559" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
         <v>32</v>
       </c>
@@ -19444,7 +19320,7 @@
         <v>242985.79282387</v>
       </c>
     </row>
-    <row r="560" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
         <v>32</v>
       </c>
@@ -19464,7 +19340,7 @@
         <v>250908.960893198</v>
       </c>
     </row>
-    <row r="561" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
         <v>32</v>
       </c>
@@ -19484,7 +19360,7 @@
         <v>442.36447729676502</v>
       </c>
     </row>
-    <row r="562" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
         <v>32</v>
       </c>
@@ -19504,7 +19380,7 @@
         <v>862842.798877717</v>
       </c>
     </row>
-    <row r="563" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
         <v>32</v>
       </c>
@@ -19524,7 +19400,7 @@
         <v>254124.43797275401</v>
       </c>
     </row>
-    <row r="564" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
         <v>32</v>
       </c>
@@ -19544,7 +19420,7 @@
         <v>227475.807401998</v>
       </c>
     </row>
-    <row r="565" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
         <v>32</v>
       </c>
@@ -19564,7 +19440,7 @@
         <v>11964.7510092354</v>
       </c>
     </row>
-    <row r="566" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
         <v>32</v>
       </c>
@@ -19584,7 +19460,7 @@
         <v>5028.47516458667</v>
       </c>
     </row>
-    <row r="567" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
         <v>32</v>
       </c>
@@ -19604,7 +19480,7 @@
         <v>383020.64762430597</v>
       </c>
     </row>
-    <row r="568" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
         <v>32</v>
       </c>
@@ -19624,7 +19500,7 @@
         <v>194717.287782903</v>
       </c>
     </row>
-    <row r="569" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
         <v>32</v>
       </c>
@@ -19644,7 +19520,7 @@
         <v>512.25286342693903</v>
       </c>
     </row>
-    <row r="570" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
         <v>32</v>
       </c>
@@ -19664,7 +19540,7 @@
         <v>15.015858937136599</v>
       </c>
     </row>
-    <row r="571" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
         <v>32</v>
       </c>
@@ -19684,7 +19560,7 @@
         <v>237462.75824793699</v>
       </c>
     </row>
-    <row r="572" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
         <v>32</v>
       </c>
@@ -19704,7 +19580,7 @@
         <v>219888.104427507</v>
       </c>
     </row>
-    <row r="573" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
         <v>32</v>
       </c>
@@ -19724,7 +19600,7 @@
         <v>255609.51946856</v>
       </c>
     </row>
-    <row r="574" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
         <v>32</v>
       </c>
@@ -19744,7 +19620,7 @@
         <v>785.57207865527596</v>
       </c>
     </row>
-    <row r="575" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
         <v>32</v>
       </c>
@@ -19764,7 +19640,7 @@
         <v>969587.31740643701</v>
       </c>
     </row>
-    <row r="576" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
         <v>32</v>
       </c>
@@ -19784,7 +19660,7 @@
         <v>409923.21231171</v>
       </c>
     </row>
-    <row r="577" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
         <v>32</v>
       </c>
@@ -19804,7 +19680,7 @@
         <v>378145.227331915</v>
       </c>
     </row>
-    <row r="578" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
         <v>32</v>
       </c>
@@ -19824,7 +19700,7 @@
         <v>6993.0457125476296</v>
       </c>
     </row>
-    <row r="579" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
         <v>32</v>
       </c>
@@ -19844,7 +19720,7 @@
         <v>7283.3689383374203</v>
       </c>
     </row>
-    <row r="580" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
         <v>32</v>
       </c>
@@ -19864,7 +19740,7 @@
         <v>452330.655580853</v>
       </c>
     </row>
-    <row r="581" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
         <v>32</v>
       </c>
@@ -19884,7 +19760,7 @@
         <v>193687.947723388</v>
       </c>
     </row>
-    <row r="582" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
         <v>32</v>
       </c>
@@ -19904,7 +19780,7 @@
         <v>994.50759732582799</v>
       </c>
     </row>
-    <row r="583" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
         <v>32</v>
       </c>
@@ -19924,7 +19800,7 @@
         <v>22.224155856885101</v>
       </c>
     </row>
-    <row r="584" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
         <v>32</v>
       </c>
@@ -19944,7 +19820,7 @@
         <v>262685.68726298399</v>
       </c>
     </row>
-    <row r="585" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
         <v>32</v>
       </c>
@@ -19964,7 +19840,7 @@
         <v>176255.883835018</v>
       </c>
     </row>
-    <row r="586" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
         <v>32</v>
       </c>
@@ -19984,7 +19860,7 @@
         <v>204358.640969331</v>
       </c>
     </row>
-    <row r="587" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
         <v>32</v>
       </c>
@@ -20004,7 +19880,7 @@
         <v>1034.1578171061999</v>
       </c>
     </row>
-    <row r="588" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
         <v>32</v>
       </c>
@@ -20024,7 +19900,7 @@
         <v>934208.08490198397</v>
       </c>
     </row>
-    <row r="589" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
         <v>32</v>
       </c>
@@ -20044,7 +19920,7 @@
         <v>418540.97609546501</v>
       </c>
     </row>
-    <row r="590" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
         <v>32</v>
       </c>
@@ -20064,7 +19940,7 @@
         <v>502911.44269076298</v>
       </c>
     </row>
-    <row r="591" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
         <v>32</v>
       </c>
@@ -20084,7 +19960,7 @@
         <v>5707.1076297483896</v>
       </c>
     </row>
-    <row r="592" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A592" t="s">
         <v>32</v>
       </c>
@@ -20104,7 +19980,7 @@
         <v>7012.9910434429603</v>
       </c>
     </row>
-    <row r="593" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
         <v>32</v>
       </c>
@@ -20124,7 +20000,7 @@
         <v>482531.84231739299</v>
       </c>
     </row>
-    <row r="594" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
         <v>32</v>
       </c>
@@ -20144,7 +20020,7 @@
         <v>165345.92556429599</v>
       </c>
     </row>
-    <row r="595" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
         <v>32</v>
       </c>
@@ -20164,7 +20040,7 @@
         <v>904.05877986459996</v>
       </c>
     </row>
-    <row r="596" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
         <v>32</v>
       </c>
@@ -20184,7 +20060,7 @@
         <v>12.4674563471824</v>
       </c>
     </row>
-    <row r="597" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
         <v>32</v>
       </c>
@@ -20204,7 +20080,7 @@
         <v>6154498.5107608</v>
       </c>
     </row>
-    <row r="598" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
         <v>32</v>
       </c>
@@ -20224,7 +20100,7 @@
         <v>16286391.073782699</v>
       </c>
     </row>
-    <row r="599" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
         <v>32</v>
       </c>
@@ -20244,7 +20120,7 @@
         <v>11394227.281271201</v>
       </c>
     </row>
-    <row r="600" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
         <v>32</v>
       </c>
@@ -20264,7 +20140,7 @@
         <v>19039.665530452501</v>
       </c>
     </row>
-    <row r="601" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
         <v>32</v>
       </c>
@@ -20284,7 +20160,7 @@
         <v>22858248.746438101</v>
       </c>
     </row>
-    <row r="602" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
         <v>32</v>
       </c>
@@ -20304,7 +20180,7 @@
         <v>8761077.1340751909</v>
       </c>
     </row>
-    <row r="603" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
         <v>32</v>
       </c>
@@ -20324,7 +20200,7 @@
         <v>9283349.0687212609</v>
       </c>
     </row>
-    <row r="604" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
         <v>32</v>
       </c>
@@ -20344,7 +20220,7 @@
         <v>55076.344903816898</v>
       </c>
     </row>
-    <row r="605" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
         <v>32</v>
       </c>
@@ -20364,7 +20240,7 @@
         <v>28874.852664628401</v>
       </c>
     </row>
-    <row r="606" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
         <v>32</v>
       </c>
@@ -20384,7 +20260,7 @@
         <v>22120400.818000499</v>
       </c>
     </row>
-    <row r="607" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
         <v>32</v>
       </c>
@@ -20404,7 +20280,7 @@
         <v>6077990.1610848196</v>
       </c>
     </row>
-    <row r="608" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
         <v>32</v>
       </c>
@@ -20424,7 +20300,7 @@
         <v>40388.599896665597</v>
       </c>
     </row>
-    <row r="609" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
         <v>32</v>
       </c>
@@ -20444,7 +20320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="610" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
         <v>32</v>
       </c>
@@ -20464,7 +20340,7 @@
         <v>6713578.9238996198</v>
       </c>
     </row>
-    <row r="611" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
         <v>32</v>
       </c>
@@ -20484,7 +20360,7 @@
         <v>14693828.602499099</v>
       </c>
     </row>
-    <row r="612" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
         <v>32</v>
       </c>
@@ -20504,7 +20380,7 @@
         <v>9810336.7950273398</v>
       </c>
     </row>
-    <row r="613" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
         <v>32</v>
       </c>
@@ -20524,7 +20400,7 @@
         <v>49933.598601594698</v>
       </c>
     </row>
-    <row r="614" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
         <v>32</v>
       </c>
@@ -20544,7 +20420,7 @@
         <v>24364394.026106201</v>
       </c>
     </row>
-    <row r="615" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
         <v>32</v>
       </c>
@@ -20564,7 +20440,7 @@
         <v>13948528.137840301</v>
       </c>
     </row>
-    <row r="616" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
         <v>32</v>
       </c>
@@ -20584,7 +20460,7 @@
         <v>7254083.7700359002</v>
       </c>
     </row>
-    <row r="617" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
         <v>32</v>
       </c>
@@ -20604,7 +20480,7 @@
         <v>312908.398940983</v>
       </c>
     </row>
-    <row r="618" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
         <v>32</v>
       </c>
@@ -20624,7 +20500,7 @@
         <v>298090.01712643699</v>
       </c>
     </row>
-    <row r="619" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
         <v>32</v>
       </c>
@@ -20644,7 +20520,7 @@
         <v>19022739.951641999</v>
       </c>
     </row>
-    <row r="620" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
         <v>32</v>
       </c>
@@ -20664,7 +20540,7 @@
         <v>5918663.6884770198</v>
       </c>
     </row>
-    <row r="621" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
         <v>32</v>
       </c>
@@ -20684,7 +20560,7 @@
         <v>137189.21836333099</v>
       </c>
     </row>
-    <row r="622" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
         <v>32</v>
       </c>
@@ -20704,7 +20580,7 @@
         <v>6308.6383693709604</v>
       </c>
     </row>
-    <row r="623" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
         <v>32</v>
       </c>
@@ -20724,7 +20600,7 @@
         <v>6329047.0030778702</v>
       </c>
     </row>
-    <row r="624" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
         <v>32</v>
       </c>
@@ -20744,7 +20620,7 @@
         <v>11364525.7076618</v>
       </c>
     </row>
-    <row r="625" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
         <v>32</v>
       </c>
@@ -20764,7 +20640,7 @@
         <v>8563549.4104688093</v>
       </c>
     </row>
-    <row r="626" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
         <v>32</v>
       </c>
@@ -20784,7 +20660,7 @@
         <v>22049.1593497875</v>
       </c>
     </row>
-    <row r="627" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
         <v>32</v>
       </c>
@@ -20804,7 +20680,7 @@
         <v>20405441.018457498</v>
       </c>
     </row>
-    <row r="628" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
         <v>32</v>
       </c>
@@ -20824,7 +20700,7 @@
         <v>6661839.2893296704</v>
       </c>
     </row>
-    <row r="629" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
         <v>32</v>
       </c>
@@ -20844,7 +20720,7 @@
         <v>10436609.249159001</v>
       </c>
     </row>
-    <row r="630" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
         <v>32</v>
       </c>
@@ -20864,7 +20740,7 @@
         <v>405562.466599526</v>
       </c>
     </row>
-    <row r="631" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
         <v>32</v>
       </c>
@@ -20884,7 +20760,7 @@
         <v>83080.435043424004</v>
       </c>
     </row>
-    <row r="632" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
         <v>32</v>
       </c>
@@ -20904,7 +20780,7 @@
         <v>18736267.451869398</v>
       </c>
     </row>
-    <row r="633" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
         <v>32</v>
       </c>
@@ -20924,7 +20800,7 @@
         <v>5583793.3059029998</v>
       </c>
     </row>
-    <row r="634" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
         <v>32</v>
       </c>
@@ -20944,7 +20820,7 @@
         <v>81119.495612850398</v>
       </c>
     </row>
-    <row r="635" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
         <v>32</v>
       </c>
@@ -20964,7 +20840,7 @@
         <v>472.78465094768001</v>
       </c>
     </row>
-    <row r="636" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
         <v>32</v>
       </c>
@@ -20984,7 +20860,7 @@
         <v>7201842.6036828998</v>
       </c>
     </row>
-    <row r="637" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
         <v>32</v>
       </c>
@@ -21004,7 +20880,7 @@
         <v>10714833.933357799</v>
       </c>
     </row>
-    <row r="638" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
         <v>32</v>
       </c>
@@ -21024,7 +20900,7 @@
         <v>9595088.6617977805</v>
       </c>
     </row>
-    <row r="639" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
         <v>32</v>
       </c>
@@ -21044,7 +20920,7 @@
         <v>30099.5691642682</v>
       </c>
     </row>
-    <row r="640" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
         <v>32</v>
       </c>
@@ -21064,7 +20940,7 @@
         <v>28448063.072431002</v>
       </c>
     </row>
-    <row r="641" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
         <v>32</v>
       </c>
@@ -21084,7 +20960,7 @@
         <v>15945554.272925301</v>
       </c>
     </row>
-    <row r="642" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
         <v>32</v>
       </c>
@@ -21104,7 +20980,7 @@
         <v>10679814.5966023</v>
       </c>
     </row>
-    <row r="643" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
         <v>32</v>
       </c>
@@ -21124,7 +21000,7 @@
         <v>344290.25556485902</v>
       </c>
     </row>
-    <row r="644" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
         <v>32</v>
       </c>
@@ -21144,7 +21020,7 @@
         <v>636412.39179768204</v>
       </c>
     </row>
-    <row r="645" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
         <v>32</v>
       </c>
@@ -21164,7 +21040,7 @@
         <v>19138283.239505202</v>
       </c>
     </row>
-    <row r="646" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
         <v>32</v>
       </c>
@@ -21184,7 +21060,7 @@
         <v>7073792.1454489604</v>
       </c>
     </row>
-    <row r="647" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
         <v>32</v>
       </c>
@@ -21204,7 +21080,7 @@
         <v>105373.151221067</v>
       </c>
     </row>
-    <row r="648" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
         <v>32</v>
       </c>
@@ -21224,7 +21100,7 @@
         <v>1423.79701655397</v>
       </c>
     </row>
-    <row r="649" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
         <v>32</v>
       </c>
@@ -21244,7 +21120,7 @@
         <v>7053263.3221524796</v>
       </c>
     </row>
-    <row r="650" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
         <v>32</v>
       </c>
@@ -21264,7 +21140,7 @@
         <v>10678674.1768174</v>
       </c>
     </row>
-    <row r="651" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A651" t="s">
         <v>32</v>
       </c>
@@ -21284,7 +21160,7 @@
         <v>11742513.071988</v>
       </c>
     </row>
-    <row r="652" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A652" t="s">
         <v>32</v>
       </c>
@@ -21304,7 +21180,7 @@
         <v>25537.000385557199</v>
       </c>
     </row>
-    <row r="653" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
         <v>32</v>
       </c>
@@ -21324,7 +21200,7 @@
         <v>33226780.9649119</v>
       </c>
     </row>
-    <row r="654" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A654" t="s">
         <v>32</v>
       </c>
@@ -21344,7 +21220,7 @@
         <v>10609691.2951237</v>
       </c>
     </row>
-    <row r="655" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
         <v>32</v>
       </c>
@@ -21364,7 +21240,7 @@
         <v>11637731.709718799</v>
       </c>
     </row>
-    <row r="656" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
         <v>32</v>
       </c>
@@ -21384,7 +21260,7 @@
         <v>743675.580063464</v>
       </c>
     </row>
-    <row r="657" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A657" t="s">
         <v>32</v>
       </c>
@@ -21404,7 +21280,7 @@
         <v>309847.10166611703</v>
       </c>
     </row>
-    <row r="658" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A658" t="s">
         <v>32</v>
       </c>
@@ -21424,7 +21300,7 @@
         <v>20040287.758719001</v>
       </c>
     </row>
-    <row r="659" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A659" t="s">
         <v>32</v>
       </c>
@@ -21444,7 +21320,7 @@
         <v>9457103.2088973094</v>
       </c>
     </row>
-    <row r="660" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A660" t="s">
         <v>32</v>
       </c>
@@ -21464,7 +21340,7 @@
         <v>17901.099686035999</v>
       </c>
     </row>
-    <row r="661" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A661" t="s">
         <v>32</v>
       </c>
@@ -21484,7 +21360,7 @@
         <v>436.28993637767798</v>
       </c>
     </row>
-    <row r="662" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A662" t="s">
         <v>32</v>
       </c>
@@ -21504,7 +21380,7 @@
         <v>7702176.8022137601</v>
       </c>
     </row>
-    <row r="663" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A663" t="s">
         <v>32</v>
       </c>
@@ -21524,7 +21400,7 @@
         <v>9700320.2451232392</v>
       </c>
     </row>
-    <row r="664" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A664" t="s">
         <v>32</v>
       </c>
@@ -21544,7 +21420,7 @@
         <v>12297200.597000699</v>
       </c>
     </row>
-    <row r="665" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A665" t="s">
         <v>32</v>
       </c>
@@ -21564,7 +21440,7 @@
         <v>41479.011455744003</v>
       </c>
     </row>
-    <row r="666" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A666" t="s">
         <v>32</v>
       </c>
@@ -21584,7 +21460,7 @@
         <v>38650898.963250503</v>
       </c>
     </row>
-    <row r="667" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A667" t="s">
         <v>32</v>
       </c>
@@ -21604,7 +21480,7 @@
         <v>19605250.039858501</v>
       </c>
     </row>
-    <row r="668" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A668" t="s">
         <v>32</v>
       </c>
@@ -21624,7 +21500,7 @@
         <v>20320921.2985074</v>
       </c>
     </row>
-    <row r="669" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A669" t="s">
         <v>32</v>
       </c>
@@ -21644,7 +21520,7 @@
         <v>415137.103054301</v>
       </c>
     </row>
-    <row r="670" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A670" t="s">
         <v>32</v>
       </c>
@@ -21664,7 +21540,7 @@
         <v>485267.65439439501</v>
       </c>
     </row>
-    <row r="671" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A671" t="s">
         <v>32</v>
       </c>
@@ -21684,7 +21560,7 @@
         <v>24430385.701804399</v>
       </c>
     </row>
-    <row r="672" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A672" t="s">
         <v>32</v>
       </c>
@@ -21704,7 +21580,7 @@
         <v>9412597.0866468102</v>
       </c>
     </row>
-    <row r="673" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A673" t="s">
         <v>32</v>
       </c>
@@ -21724,7 +21600,7 @@
         <v>35166.9396222059</v>
       </c>
     </row>
-    <row r="674" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A674" t="s">
         <v>32</v>
       </c>
@@ -21744,7 +21620,7 @@
         <v>1324.56606195885</v>
       </c>
     </row>
-    <row r="675" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A675" t="s">
         <v>32</v>
       </c>
@@ -21764,7 +21640,7 @@
         <v>8772621.7394210994</v>
       </c>
     </row>
-    <row r="676" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A676" t="s">
         <v>32</v>
       </c>
@@ -21784,7 +21660,7 @@
         <v>7827153.1616754802</v>
       </c>
     </row>
-    <row r="677" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A677" t="s">
         <v>32</v>
       </c>
@@ -21804,7 +21680,7 @@
         <v>9846941.1624757499</v>
       </c>
     </row>
-    <row r="678" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A678" t="s">
         <v>32</v>
       </c>
@@ -21824,7 +21700,7 @@
         <v>55920.318228686898</v>
       </c>
     </row>
-    <row r="679" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A679" t="s">
         <v>32</v>
       </c>
@@ -21844,7 +21720,7 @@
         <v>37588453.734635003</v>
       </c>
     </row>
-    <row r="680" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A680" t="s">
         <v>32</v>
       </c>
@@ -21864,7 +21740,7 @@
         <v>18951665.913834602</v>
       </c>
     </row>
-    <row r="681" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A681" t="s">
         <v>32</v>
       </c>
@@ -21884,7 +21760,7 @@
         <v>26362524.643263198</v>
       </c>
     </row>
-    <row r="682" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A682" t="s">
         <v>32</v>
       </c>
@@ -21904,7 +21780,7 @@
         <v>314240.04259316198</v>
       </c>
     </row>
-    <row r="683" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A683" t="s">
         <v>32</v>
       </c>
@@ -21924,7 +21800,7 @@
         <v>399529.237170109</v>
       </c>
     </row>
-    <row r="684" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A684" t="s">
         <v>32</v>
       </c>
@@ -21944,7 +21820,7 @@
         <v>26006548.998320799</v>
       </c>
     </row>
-    <row r="685" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A685" t="s">
         <v>32</v>
       </c>
@@ -21964,7 +21840,7 @@
         <v>8160697.5309893098</v>
       </c>
     </row>
-    <row r="686" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A686" t="s">
         <v>32</v>
       </c>
@@ -21984,7 +21860,7 @@
         <v>28867.8868426685</v>
       </c>
     </row>
-    <row r="687" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A687" t="s">
         <v>32</v>
       </c>
@@ -22004,7 +21880,7 @@
         <v>834.68647590212402</v>
       </c>
     </row>
-    <row r="688" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A688" t="s">
         <v>32</v>
       </c>
@@ -22024,7 +21900,7 @@
         <v>51141.712543276197</v>
       </c>
     </row>
-    <row r="689" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A689" t="s">
         <v>32</v>
       </c>
@@ -22044,7 +21920,7 @@
         <v>117252.511445228</v>
       </c>
     </row>
-    <row r="690" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A690" t="s">
         <v>32</v>
       </c>
@@ -22064,7 +21940,7 @@
         <v>69554.703748519998</v>
       </c>
     </row>
-    <row r="691" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A691" t="s">
         <v>32</v>
       </c>
@@ -22084,7 +21960,7 @@
         <v>110.088791680744</v>
       </c>
     </row>
-    <row r="692" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A692" t="s">
         <v>32</v>
       </c>
@@ -22104,7 +21980,7 @@
         <v>158233.03235165699</v>
       </c>
     </row>
-    <row r="693" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A693" t="s">
         <v>32</v>
       </c>
@@ -22124,7 +22000,7 @@
         <v>47032.414672640698</v>
       </c>
     </row>
-    <row r="694" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A694" t="s">
         <v>32</v>
       </c>
@@ -22144,7 +22020,7 @@
         <v>50770.609025541999</v>
       </c>
     </row>
-    <row r="695" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A695" t="s">
         <v>32</v>
       </c>
@@ -22164,7 +22040,7 @@
         <v>344.94642259084702</v>
       </c>
     </row>
-    <row r="696" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A696" t="s">
         <v>32</v>
       </c>
@@ -22184,7 +22060,7 @@
         <v>198.302146517034</v>
       </c>
     </row>
-    <row r="697" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A697" t="s">
         <v>32</v>
       </c>
@@ -22204,7 +22080,7 @@
         <v>117832.856609358</v>
       </c>
     </row>
-    <row r="698" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A698" t="s">
         <v>32</v>
       </c>
@@ -22224,7 +22100,7 @@
         <v>37538.119750412297</v>
       </c>
     </row>
-    <row r="699" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A699" t="s">
         <v>32</v>
       </c>
@@ -22244,7 +22120,7 @@
         <v>367.91249801908702</v>
       </c>
     </row>
-    <row r="700" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A700" t="s">
         <v>32</v>
       </c>
@@ -22264,7 +22140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="701" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A701" t="s">
         <v>32</v>
       </c>
@@ -22284,7 +22160,7 @@
         <v>59183.111683406198</v>
       </c>
     </row>
-    <row r="702" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A702" t="s">
         <v>32</v>
       </c>
@@ -22304,7 +22180,7 @@
         <v>95901.894301370397</v>
       </c>
     </row>
-    <row r="703" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A703" t="s">
         <v>32</v>
       </c>
@@ -22324,7 +22200,7 @@
         <v>59472.022241057901</v>
       </c>
     </row>
-    <row r="704" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A704" t="s">
         <v>32</v>
       </c>
@@ -22344,7 +22220,7 @@
         <v>256.44721760956099</v>
       </c>
     </row>
-    <row r="705" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A705" t="s">
         <v>32</v>
       </c>
@@ -22364,7 +22240,7 @@
         <v>170575.08553377399</v>
       </c>
     </row>
-    <row r="706" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A706" t="s">
         <v>32</v>
       </c>
@@ -22384,7 +22260,7 @@
         <v>96339.443855501202</v>
       </c>
     </row>
-    <row r="707" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A707" t="s">
         <v>32</v>
       </c>
@@ -22404,7 +22280,7 @@
         <v>39697.737834622501</v>
       </c>
     </row>
-    <row r="708" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A708" t="s">
         <v>32</v>
       </c>
@@ -22424,7 +22300,7 @@
         <v>1605.0785659872799</v>
       </c>
     </row>
-    <row r="709" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A709" t="s">
         <v>32</v>
       </c>
@@ -22444,7 +22320,7 @@
         <v>1990.9654255017001</v>
       </c>
     </row>
-    <row r="710" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A710" t="s">
         <v>32</v>
       </c>
@@ -22464,7 +22340,7 @@
         <v>100956.588625463</v>
       </c>
     </row>
-    <row r="711" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A711" t="s">
         <v>32</v>
       </c>
@@ -22484,7 +22360,7 @@
         <v>34686.349652746801</v>
       </c>
     </row>
-    <row r="712" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A712" t="s">
         <v>32</v>
       </c>
@@ -22504,7 +22380,7 @@
         <v>1128.79583384987</v>
       </c>
     </row>
-    <row r="713" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A713" t="s">
         <v>32</v>
       </c>
@@ -22524,7 +22400,7 @@
         <v>29.971801597069799</v>
       </c>
     </row>
-    <row r="714" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A714" t="s">
         <v>32</v>
       </c>
@@ -22544,7 +22420,7 @@
         <v>54586.395934530403</v>
       </c>
     </row>
-    <row r="715" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A715" t="s">
         <v>32</v>
       </c>
@@ -22564,7 +22440,7 @@
         <v>74900.490533014701</v>
       </c>
     </row>
-    <row r="716" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A716" t="s">
         <v>32</v>
       </c>
@@ -22584,7 +22460,7 @@
         <v>49865.969402181101</v>
       </c>
     </row>
-    <row r="717" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A717" t="s">
         <v>32</v>
       </c>
@@ -22604,7 +22480,7 @@
         <v>110.281107187057</v>
       </c>
     </row>
-    <row r="718" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A718" t="s">
         <v>32</v>
       </c>
@@ -22624,7 +22500,7 @@
         <v>147118.664474658</v>
       </c>
     </row>
-    <row r="719" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A719" t="s">
         <v>32</v>
       </c>
@@ -22644,7 +22520,7 @@
         <v>36729.964594335099</v>
       </c>
     </row>
-    <row r="720" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A720" t="s">
         <v>32</v>
       </c>
@@ -22664,7 +22540,7 @@
         <v>56817.361764666603</v>
       </c>
     </row>
-    <row r="721" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A721" t="s">
         <v>32</v>
       </c>
@@ -22684,7 +22560,7 @@
         <v>1838.2008145433999</v>
       </c>
     </row>
-    <row r="722" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A722" t="s">
         <v>32</v>
       </c>
@@ -22704,7 +22580,7 @@
         <v>612.604102482141</v>
       </c>
     </row>
-    <row r="723" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A723" t="s">
         <v>32</v>
       </c>
@@ -22724,7 +22600,7 @@
         <v>99425.071141673005</v>
       </c>
     </row>
-    <row r="724" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A724" t="s">
         <v>32</v>
       </c>
@@ -22744,7 +22620,7 @@
         <v>32225.117246266698</v>
       </c>
     </row>
-    <row r="725" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A725" t="s">
         <v>32</v>
       </c>
@@ -22764,7 +22640,7 @@
         <v>712.89346602129501</v>
       </c>
     </row>
-    <row r="726" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A726" t="s">
         <v>32</v>
       </c>
@@ -22784,7 +22660,7 @@
         <v>2.22376803394706</v>
       </c>
     </row>
-    <row r="727" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A727" t="s">
         <v>32</v>
       </c>
@@ -22804,7 +22680,7 @@
         <v>61949.367727396297</v>
       </c>
     </row>
-    <row r="728" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A728" t="s">
         <v>32</v>
       </c>
@@ -22824,7 +22700,7 @@
         <v>68421.1021087236</v>
       </c>
     </row>
-    <row r="729" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A729" t="s">
         <v>32</v>
       </c>
@@ -22844,7 +22720,7 @@
         <v>57159.165980288599</v>
       </c>
     </row>
-    <row r="730" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A730" t="s">
         <v>32</v>
       </c>
@@ -22864,7 +22740,7 @@
         <v>156.738441276673</v>
       </c>
     </row>
-    <row r="731" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A731" t="s">
         <v>32</v>
       </c>
@@ -22884,7 +22760,7 @@
         <v>185374.91191267801</v>
       </c>
     </row>
-    <row r="732" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A732" t="s">
         <v>32</v>
       </c>
@@ -22904,7 +22780,7 @@
         <v>106118.35202358699</v>
       </c>
     </row>
-    <row r="733" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A733" t="s">
         <v>32</v>
       </c>
@@ -22924,7 +22800,7 @@
         <v>58373.8168224693</v>
       </c>
     </row>
-    <row r="734" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A734" t="s">
         <v>32</v>
       </c>
@@ -22944,7 +22820,7 @@
         <v>1588.6795265010401</v>
       </c>
     </row>
-    <row r="735" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A735" t="s">
         <v>32</v>
       </c>
@@ -22964,7 +22840,7 @@
         <v>3223.9972162877898</v>
       </c>
     </row>
-    <row r="736" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A736" t="s">
         <v>32</v>
       </c>
@@ -22984,7 +22860,7 @@
         <v>101219.188317972</v>
       </c>
     </row>
-    <row r="737" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A737" t="s">
         <v>32</v>
       </c>
@@ -23004,7 +22880,7 @@
         <v>41592.166429896497</v>
       </c>
     </row>
-    <row r="738" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A738" t="s">
         <v>32</v>
       </c>
@@ -23024,7 +22900,7 @@
         <v>951.271047775341</v>
       </c>
     </row>
-    <row r="739" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A739" t="s">
         <v>32</v>
       </c>
@@ -23044,7 +22920,7 @@
         <v>11.1192365832293</v>
       </c>
     </row>
-    <row r="740" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A740" t="s">
         <v>32</v>
       </c>
@@ -23064,7 +22940,7 @@
         <v>58826.5801459754</v>
       </c>
     </row>
-    <row r="741" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A741" t="s">
         <v>32</v>
       </c>
@@ -23084,7 +22960,7 @@
         <v>67637.851994039404</v>
       </c>
     </row>
-    <row r="742" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A742" t="s">
         <v>32</v>
       </c>
@@ -23104,7 +22980,7 @@
         <v>69843.355710816701</v>
       </c>
     </row>
-    <row r="743" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A743" t="s">
         <v>32</v>
       </c>
@@ -23124,7 +23000,7 @@
         <v>123.137170676095</v>
       </c>
     </row>
-    <row r="744" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A744" t="s">
         <v>32</v>
       </c>
@@ -23144,7 +23020,7 @@
         <v>240182.08162037301</v>
       </c>
     </row>
-    <row r="745" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A745" t="s">
         <v>32</v>
       </c>
@@ -23164,7 +23040,7 @@
         <v>70738.420234012301</v>
       </c>
     </row>
-    <row r="746" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A746" t="s">
         <v>32</v>
       </c>
@@ -23184,7 +23060,7 @@
         <v>63320.471598245502</v>
       </c>
     </row>
-    <row r="747" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A747" t="s">
         <v>32</v>
       </c>
@@ -23204,7 +23080,7 @@
         <v>3330.5241779909502</v>
       </c>
     </row>
-    <row r="748" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A748" t="s">
         <v>32</v>
       </c>
@@ -23224,7 +23100,7 @@
         <v>1399.73310778936</v>
       </c>
     </row>
-    <row r="749" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A749" t="s">
         <v>32</v>
       </c>
@@ -23244,7 +23120,7 @@
         <v>106618.142458446</v>
       </c>
     </row>
-    <row r="750" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A750" t="s">
         <v>32</v>
       </c>
@@ -23264,7 +23140,7 @@
         <v>54201.766032005296</v>
       </c>
     </row>
-    <row r="751" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A751" t="s">
         <v>32</v>
       </c>
@@ -23284,7 +23160,7 @@
         <v>142.591395806869</v>
       </c>
     </row>
-    <row r="752" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A752" t="s">
         <v>32</v>
       </c>
@@ -23304,7 +23180,7 @@
         <v>4.1798346831315101</v>
       </c>
     </row>
-    <row r="753" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A753" t="s">
         <v>32</v>
       </c>
@@ -23324,7 +23200,7 @@
         <v>66100.452663554097</v>
       </c>
     </row>
-    <row r="754" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A754" t="s">
         <v>32</v>
       </c>
@@ -23344,7 +23220,7 @@
         <v>61208.348396312402</v>
       </c>
     </row>
-    <row r="755" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A755" t="s">
         <v>32</v>
       </c>
@@ -23364,7 +23240,7 @@
         <v>71151.809515933201</v>
       </c>
     </row>
-    <row r="756" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A756" t="s">
         <v>32</v>
       </c>
@@ -23384,7 +23260,7 @@
         <v>218.67290004584899</v>
       </c>
     </row>
-    <row r="757" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A757" t="s">
         <v>32</v>
       </c>
@@ -23404,7 +23280,7 @@
         <v>269895.62932007102</v>
       </c>
     </row>
-    <row r="758" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A758" t="s">
         <v>32</v>
       </c>
@@ -23424,7 +23300,7 @@
         <v>114106.77653634999</v>
       </c>
     </row>
-    <row r="759" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A759" t="s">
         <v>32</v>
       </c>
@@ -23444,7 +23320,7 @@
         <v>105261.013910672</v>
       </c>
     </row>
-    <row r="760" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A760" t="s">
         <v>32</v>
       </c>
@@ -23464,7 +23340,7 @@
         <v>1946.5936069591501</v>
       </c>
     </row>
-    <row r="761" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A761" t="s">
         <v>32</v>
       </c>
@@ -23484,7 +23360,7 @@
         <v>2027.40837044056</v>
       </c>
     </row>
-    <row r="762" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A762" t="s">
         <v>32</v>
       </c>
@@ -23504,7 +23380,7 @@
         <v>125911.369463158</v>
       </c>
     </row>
-    <row r="763" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A763" t="s">
         <v>32</v>
       </c>
@@ -23524,7 +23400,7 @@
         <v>53915.237549052203</v>
       </c>
     </row>
-    <row r="764" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A764" t="s">
         <v>32</v>
       </c>
@@ -23544,7 +23420,7 @@
         <v>276.83247194468902</v>
       </c>
     </row>
-    <row r="765" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A765" t="s">
         <v>32</v>
       </c>
@@ -23564,7 +23440,7 @@
         <v>6.1863459055405103</v>
       </c>
     </row>
-    <row r="766" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A766" t="s">
         <v>32</v>
       </c>
@@ -23584,7 +23460,7 @@
         <v>73121.541097364199</v>
       </c>
     </row>
-    <row r="767" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A767" t="s">
         <v>32</v>
       </c>
@@ -23604,7 +23480,7 @@
         <v>49062.824807016499</v>
       </c>
     </row>
-    <row r="768" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A768" t="s">
         <v>32</v>
       </c>
@@ -23624,7 +23500,7 @@
         <v>56885.5460681482</v>
       </c>
     </row>
-    <row r="769" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A769" t="s">
         <v>32</v>
       </c>
@@ -23644,7 +23520,7 @@
         <v>287.86956043397498</v>
       </c>
     </row>
-    <row r="770" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A770" t="s">
         <v>32</v>
       </c>
@@ -23664,7 +23540,7 @@
         <v>260047.41859141199</v>
       </c>
     </row>
-    <row r="771" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A771" t="s">
         <v>32</v>
       </c>
@@ -23684,7 +23560,7 @@
         <v>116505.628850104</v>
       </c>
     </row>
-    <row r="772" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A772" t="s">
         <v>32</v>
       </c>
@@ -23704,7 +23580,7 @@
         <v>139991.105370854</v>
       </c>
     </row>
-    <row r="773" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A773" t="s">
         <v>32</v>
       </c>
@@ -23724,7 +23600,7 @@
         <v>1588.63815323878</v>
       </c>
     </row>
-    <row r="774" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A774" t="s">
         <v>32</v>
       </c>
@@ -23744,7 +23620,7 @@
         <v>1952.14561608444</v>
       </c>
     </row>
-    <row r="775" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A775" t="s">
         <v>32</v>
       </c>
@@ -23764,7 +23640,7 @@
         <v>134318.212409773</v>
       </c>
     </row>
-    <row r="776" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A776" t="s">
         <v>32</v>
       </c>
@@ -23784,7 +23660,7 @@
         <v>46025.914153926897</v>
       </c>
     </row>
-    <row r="777" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A777" t="s">
         <v>32</v>
       </c>
@@ -23804,7 +23680,7 @@
         <v>251.65501750432699</v>
       </c>
     </row>
-    <row r="778" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A778" t="s">
         <v>32</v>
       </c>
@@ -23824,7 +23700,7 @@
         <v>3.4704579117682202</v>
       </c>
     </row>
-    <row r="779" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A779" t="s">
         <v>38</v>
       </c>
@@ -23844,7 +23720,7 @@
         <v>178187.32426754199</v>
       </c>
     </row>
-    <row r="780" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A780" t="s">
         <v>38</v>
       </c>
@@ -23864,7 +23740,7 @@
         <v>92931.281791483096</v>
       </c>
     </row>
-    <row r="781" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A781" t="s">
         <v>38</v>
       </c>
@@ -23884,7 +23760,7 @@
         <v>22361.728964992999</v>
       </c>
     </row>
-    <row r="782" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A782" t="s">
         <v>38</v>
       </c>
@@ -23904,7 +23780,7 @@
         <v>284056.17673785501</v>
       </c>
     </row>
-    <row r="783" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A783" t="s">
         <v>38</v>
       </c>
@@ -23924,7 +23800,7 @@
         <v>2535938.1711519998</v>
       </c>
     </row>
-    <row r="784" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A784" t="s">
         <v>38</v>
       </c>
@@ -23944,7 +23820,7 @@
         <v>864664.334912939</v>
       </c>
     </row>
-    <row r="785" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A785" t="s">
         <v>38</v>
       </c>
@@ -23964,7 +23840,7 @@
         <v>259746.09646131599</v>
       </c>
     </row>
-    <row r="786" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A786" t="s">
         <v>38</v>
       </c>
@@ -23984,7 +23860,7 @@
         <v>6136315.8852999602</v>
       </c>
     </row>
-    <row r="787" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A787" t="s">
         <v>38</v>
       </c>
@@ -24004,7 +23880,7 @@
         <v>5593315.5896220403</v>
       </c>
     </row>
-    <row r="788" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A788" t="s">
         <v>38</v>
       </c>
@@ -24024,7 +23900,7 @@
         <v>493179.88277529401</v>
       </c>
     </row>
-    <row r="789" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A789" t="s">
         <v>38</v>
       </c>
@@ -24044,7 +23920,7 @@
         <v>948916.98352311901</v>
       </c>
     </row>
-    <row r="790" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A790" t="s">
         <v>38</v>
       </c>
@@ -24064,7 +23940,7 @@
         <v>3571021.1312151402</v>
       </c>
     </row>
-    <row r="791" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A791" t="s">
         <v>38</v>
       </c>
@@ -24084,7 +23960,7 @@
         <v>5954832.5539094498</v>
       </c>
     </row>
-    <row r="792" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A792" t="s">
         <v>38</v>
       </c>
@@ -24104,7 +23980,7 @@
         <v>4965813.7604759503</v>
       </c>
     </row>
-    <row r="793" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A793" t="s">
         <v>38</v>
       </c>
@@ -24124,7 +24000,7 @@
         <v>4525976.52474235</v>
       </c>
     </row>
-    <row r="794" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A794" t="s">
         <v>38</v>
       </c>
@@ -24144,7 +24020,7 @@
         <v>366514.58964982798</v>
       </c>
     </row>
-    <row r="795" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A795" t="s">
         <v>38</v>
       </c>
@@ -24164,7 +24040,7 @@
         <v>61911.010567588601</v>
       </c>
     </row>
-    <row r="796" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A796" t="s">
         <v>38</v>
       </c>
@@ -24184,7 +24060,7 @@
         <v>86029.739264136399</v>
       </c>
     </row>
-    <row r="797" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A797" t="s">
         <v>38</v>
       </c>
@@ -24204,7 +24080,7 @@
         <v>556856.61358147894</v>
       </c>
     </row>
-    <row r="798" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A798" t="s">
         <v>38</v>
       </c>
@@ -24224,7 +24100,7 @@
         <v>2312422.4132307102</v>
       </c>
     </row>
-    <row r="799" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A799" t="s">
         <v>38</v>
       </c>
@@ -24244,7 +24120,7 @@
         <v>311232.69791973499</v>
       </c>
     </row>
-    <row r="800" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A800" t="s">
         <v>38</v>
       </c>
@@ -24264,7 +24140,7 @@
         <v>636648.83858568396</v>
       </c>
     </row>
-    <row r="801" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A801" t="s">
         <v>38</v>
       </c>
@@ -24284,7 +24160,7 @@
         <v>7251360.7591710798</v>
       </c>
     </row>
-    <row r="802" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A802" t="s">
         <v>38</v>
       </c>
@@ -24304,7 +24180,7 @@
         <v>14789762.8616687</v>
       </c>
     </row>
-    <row r="803" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A803" t="s">
         <v>38</v>
       </c>
@@ -24324,7 +24200,7 @@
         <v>812882.79556647397</v>
       </c>
     </row>
-    <row r="804" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A804" t="s">
         <v>38</v>
       </c>
@@ -24344,7 +24220,7 @@
         <v>693855.42954954901</v>
       </c>
     </row>
-    <row r="805" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A805" t="s">
         <v>38</v>
       </c>
@@ -24364,7 +24240,7 @@
         <v>1612888.59358429</v>
       </c>
     </row>
-    <row r="806" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A806" t="s">
         <v>38</v>
       </c>
@@ -24384,7 +24260,7 @@
         <v>6692220.9905293398</v>
       </c>
     </row>
-    <row r="807" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A807" t="s">
         <v>38</v>
       </c>
@@ -24404,7 +24280,7 @@
         <v>6606174.8729589302</v>
       </c>
     </row>
-    <row r="808" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A808" t="s">
         <v>38</v>
       </c>
@@ -24424,7 +24300,7 @@
         <v>2551239.3399604601</v>
       </c>
     </row>
-    <row r="809" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A809" t="s">
         <v>38</v>
       </c>
@@ -24444,7 +24320,7 @@
         <v>166238.986488914</v>
       </c>
     </row>
-    <row r="810" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A810" t="s">
         <v>38</v>
       </c>
@@ -24464,7 +24340,7 @@
         <v>13668.921799812601</v>
       </c>
     </row>
-    <row r="811" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A811" t="s">
         <v>38</v>
       </c>
@@ -24484,7 +24360,7 @@
         <v>36059.7272349048</v>
       </c>
     </row>
-    <row r="812" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A812" t="s">
         <v>38</v>
       </c>
@@ -24504,7 +24380,7 @@
         <v>30875.919662016298</v>
       </c>
     </row>
-    <row r="813" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A813" t="s">
         <v>38</v>
       </c>
@@ -24524,7 +24400,7 @@
         <v>1375483.6957296701</v>
       </c>
     </row>
-    <row r="814" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A814" t="s">
         <v>38</v>
       </c>
@@ -24544,7 +24420,7 @@
         <v>295722.548989998</v>
       </c>
     </row>
-    <row r="815" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A815" t="s">
         <v>38</v>
       </c>
@@ -24564,7 +24440,7 @@
         <v>200821.657440882</v>
       </c>
     </row>
-    <row r="816" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A816" t="s">
         <v>38</v>
       </c>
@@ -24584,7 +24460,7 @@
         <v>12609792.6664172</v>
       </c>
     </row>
-    <row r="817" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A817" t="s">
         <v>38</v>
       </c>
@@ -24604,7 +24480,7 @@
         <v>9824311.0279441606</v>
       </c>
     </row>
-    <row r="818" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A818" t="s">
         <v>38</v>
       </c>
@@ -24624,7 +24500,7 @@
         <v>2215515.6308631701</v>
       </c>
     </row>
-    <row r="819" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A819" t="s">
         <v>38</v>
       </c>
@@ -24644,7 +24520,7 @@
         <v>316111.17539759702</v>
       </c>
     </row>
-    <row r="820" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A820" t="s">
         <v>38</v>
       </c>
@@ -24664,7 +24540,7 @@
         <v>1011586.34454096</v>
       </c>
     </row>
-    <row r="821" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A821" t="s">
         <v>38</v>
       </c>
@@ -24684,7 +24560,7 @@
         <v>5297030.4765440496</v>
       </c>
     </row>
-    <row r="822" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A822" t="s">
         <v>38</v>
       </c>
@@ -24704,7 +24580,7 @@
         <v>4084132.1382716498</v>
       </c>
     </row>
-    <row r="823" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A823" t="s">
         <v>38</v>
       </c>
@@ -24724,7 +24600,7 @@
         <v>1861960.46878318</v>
       </c>
     </row>
-    <row r="824" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A824" t="s">
         <v>38</v>
       </c>
@@ -24744,7 +24620,7 @@
         <v>260637.23214082001</v>
       </c>
     </row>
-    <row r="825" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A825" t="s">
         <v>38</v>
       </c>
@@ -24764,7 +24640,7 @@
         <v>27498.3986278997</v>
       </c>
     </row>
-    <row r="826" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A826" t="s">
         <v>38</v>
       </c>
@@ -24784,7 +24660,7 @@
         <v>32874.026057844399</v>
       </c>
     </row>
-    <row r="827" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A827" t="s">
         <v>38</v>
       </c>
@@ -24804,7 +24680,7 @@
         <v>76447.327728143297</v>
       </c>
     </row>
-    <row r="828" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A828" t="s">
         <v>38</v>
       </c>
@@ -24824,7 +24700,7 @@
         <v>1099388.2672006399</v>
       </c>
     </row>
-    <row r="829" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A829" t="s">
         <v>38</v>
       </c>
@@ -24844,7 +24720,7 @@
         <v>687753.34509978699</v>
       </c>
     </row>
-    <row r="830" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A830" t="s">
         <v>38</v>
       </c>
@@ -24864,7 +24740,7 @@
         <v>876339.72974353598</v>
       </c>
     </row>
-    <row r="831" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A831" t="s">
         <v>38</v>
       </c>
@@ -24884,7 +24760,7 @@
         <v>4408147.6594774202</v>
       </c>
     </row>
-    <row r="832" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A832" t="s">
         <v>38</v>
       </c>
@@ -24904,7 +24780,7 @@
         <v>6394768.8199346997</v>
       </c>
     </row>
-    <row r="833" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A833" t="s">
         <v>38</v>
       </c>
@@ -24924,7 +24800,7 @@
         <v>1104168.6326758401</v>
       </c>
     </row>
-    <row r="834" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A834" t="s">
         <v>38</v>
       </c>
@@ -24944,7 +24820,7 @@
         <v>436514.754314886</v>
       </c>
     </row>
-    <row r="835" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A835" t="s">
         <v>38</v>
       </c>
@@ -24964,7 +24840,7 @@
         <v>1182223.9199618399</v>
       </c>
     </row>
-    <row r="836" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A836" t="s">
         <v>38</v>
       </c>
@@ -24984,7 +24860,7 @@
         <v>2968015.52792372</v>
       </c>
     </row>
-    <row r="837" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A837" t="s">
         <v>38</v>
       </c>
@@ -25004,7 +24880,7 @@
         <v>1968332.1206678699</v>
       </c>
     </row>
-    <row r="838" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A838" t="s">
         <v>38</v>
       </c>
@@ -25024,7 +24900,7 @@
         <v>1925433.0679491099</v>
       </c>
     </row>
-    <row r="839" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A839" t="s">
         <v>38</v>
       </c>
@@ -25044,7 +24920,7 @@
         <v>188406.565743488</v>
       </c>
     </row>
-    <row r="840" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A840" t="s">
         <v>38</v>
       </c>
@@ -25064,7 +24940,7 @@
         <v>36196.812878254503</v>
       </c>
     </row>
-    <row r="841" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A841" t="s">
         <v>38</v>
       </c>
@@ -25084,7 +24960,7 @@
         <v>34701.225180642097</v>
       </c>
     </row>
-    <row r="842" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A842" t="s">
         <v>38</v>
       </c>
@@ -25104,7 +24980,7 @@
         <v>108107.772225263</v>
       </c>
     </row>
-    <row r="843" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A843" t="s">
         <v>38</v>
       </c>
@@ -25124,7 +25000,7 @@
         <v>720410.88511957705</v>
       </c>
     </row>
-    <row r="844" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A844" t="s">
         <v>38</v>
       </c>
@@ -25144,7 +25020,7 @@
         <v>276843.76831734402</v>
       </c>
     </row>
-    <row r="845" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A845" t="s">
         <v>38</v>
       </c>
@@ -25164,7 +25040,7 @@
         <v>136209.36486067</v>
       </c>
     </row>
-    <row r="846" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A846" t="s">
         <v>38</v>
       </c>
@@ -25184,7 +25060,7 @@
         <v>5515553.8148150304</v>
       </c>
     </row>
-    <row r="847" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A847" t="s">
         <v>38</v>
       </c>
@@ -25204,7 +25080,7 @@
         <v>8387115.0794751197</v>
       </c>
     </row>
-    <row r="848" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A848" t="s">
         <v>38</v>
       </c>
@@ -25224,7 +25100,7 @@
         <v>1450908.9442082001</v>
       </c>
     </row>
-    <row r="849" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A849" t="s">
         <v>38</v>
       </c>
@@ -25244,7 +25120,7 @@
         <v>349026.73210692097</v>
       </c>
     </row>
-    <row r="850" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A850" t="s">
         <v>38</v>
       </c>
@@ -25264,7 +25140,7 @@
         <v>938598.52587679599</v>
       </c>
     </row>
-    <row r="851" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A851" t="s">
         <v>38</v>
       </c>
@@ -25284,7 +25160,7 @@
         <v>5421476.4593969099</v>
       </c>
     </row>
-    <row r="852" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A852" t="s">
         <v>38</v>
       </c>
@@ -25304,7 +25180,7 @@
         <v>2650418.9501065798</v>
       </c>
     </row>
-    <row r="853" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A853" t="s">
         <v>38</v>
       </c>
@@ -25324,7 +25200,7 @@
         <v>2527022.5593117001</v>
       </c>
     </row>
-    <row r="854" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A854" t="s">
         <v>38</v>
       </c>
@@ -25344,7 +25220,7 @@
         <v>309219.033432119</v>
       </c>
     </row>
-    <row r="855" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A855" t="s">
         <v>38</v>
       </c>
@@ -25364,7 +25240,7 @@
         <v>17000.871621746101</v>
       </c>
     </row>
-    <row r="856" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A856" t="s">
         <v>38</v>
       </c>
@@ -25384,7 +25260,7 @@
         <v>8056.3345969038501</v>
       </c>
     </row>
-    <row r="857" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A857" t="s">
         <v>38</v>
       </c>
@@ -25404,7 +25280,7 @@
         <v>81410.438364459202</v>
       </c>
     </row>
-    <row r="858" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A858" t="s">
         <v>38</v>
       </c>
@@ -25424,7 +25300,7 @@
         <v>718488.53806203103</v>
       </c>
     </row>
-    <row r="859" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A859" t="s">
         <v>38</v>
       </c>
@@ -25444,7 +25320,7 @@
         <v>298725.72858570801</v>
       </c>
     </row>
-    <row r="860" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A860" t="s">
         <v>38</v>
       </c>
@@ -25464,7 +25340,7 @@
         <v>246503.62139384099</v>
       </c>
     </row>
-    <row r="861" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A861" t="s">
         <v>38</v>
       </c>
@@ -25484,7 +25360,7 @@
         <v>12916615.293309599</v>
       </c>
     </row>
-    <row r="862" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A862" t="s">
         <v>38</v>
       </c>
@@ -25504,7 +25380,7 @@
         <v>10174371.927360499</v>
       </c>
     </row>
-    <row r="863" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A863" t="s">
         <v>38</v>
       </c>
@@ -25524,7 +25400,7 @@
         <v>902018.94112929294</v>
       </c>
     </row>
-    <row r="864" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A864" t="s">
         <v>38</v>
       </c>
@@ -25544,7 +25420,7 @@
         <v>220860.84426706101</v>
       </c>
     </row>
-    <row r="865" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A865" t="s">
         <v>38</v>
       </c>
@@ -25564,7 +25440,7 @@
         <v>893587.23908096505</v>
       </c>
     </row>
-    <row r="866" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A866" t="s">
         <v>38</v>
       </c>
@@ -25584,7 +25460,7 @@
         <v>4941879.2004547799</v>
       </c>
     </row>
-    <row r="867" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A867" t="s">
         <v>38</v>
       </c>
@@ -25604,7 +25480,7 @@
         <v>3533394.3525197501</v>
       </c>
     </row>
-    <row r="868" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A868" t="s">
         <v>38</v>
       </c>
@@ -25624,7 +25500,7 @@
         <v>2303950.38157957</v>
       </c>
     </row>
-    <row r="869" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A869" t="s">
         <v>38</v>
       </c>
@@ -25644,7 +25520,7 @@
         <v>188014.71528410201</v>
       </c>
     </row>
-    <row r="870" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A870" t="s">
         <v>38</v>
       </c>
@@ -25664,7 +25540,7 @@
         <v>16583.8738729668</v>
       </c>
     </row>
-    <row r="871" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A871" t="s">
         <v>38</v>
       </c>
@@ -25684,7 +25560,7 @@
         <v>49745.836343839699</v>
       </c>
     </row>
-    <row r="872" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A872" t="s">
         <v>38</v>
       </c>
@@ -25704,7 +25580,7 @@
         <v>77722.962574179197</v>
       </c>
     </row>
-    <row r="873" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A873" t="s">
         <v>38</v>
       </c>
@@ -25724,7 +25600,7 @@
         <v>869729.91400319501</v>
       </c>
     </row>
-    <row r="874" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A874" t="s">
         <v>38</v>
       </c>
@@ -25744,7 +25620,7 @@
         <v>379414.02530303702</v>
       </c>
     </row>
-    <row r="875" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A875" t="s">
         <v>38</v>
       </c>
@@ -25764,7 +25640,7 @@
         <v>393012.16047680198</v>
       </c>
     </row>
-    <row r="876" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A876" t="s">
         <v>38</v>
       </c>
@@ -25784,7 +25660,7 @@
         <v>6489750.4285508096</v>
       </c>
     </row>
-    <row r="877" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A877" t="s">
         <v>38</v>
       </c>
@@ -25804,7 +25680,7 @@
         <v>8775595.8026015405</v>
       </c>
     </row>
-    <row r="878" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A878" t="s">
         <v>38</v>
       </c>
@@ -25824,7 +25700,7 @@
         <v>965662.16675917199</v>
       </c>
     </row>
-    <row r="879" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A879" t="s">
         <v>38</v>
       </c>
@@ -25844,7 +25720,7 @@
         <v>363290.90897133999</v>
       </c>
     </row>
-    <row r="880" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A880" t="s">
         <v>38</v>
       </c>
@@ -25864,7 +25740,7 @@
         <v>558656.32136020798</v>
       </c>
     </row>
-    <row r="881" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A881" t="s">
         <v>38</v>
       </c>
@@ -25884,7 +25760,7 @@
         <v>2370420.6052550399</v>
       </c>
     </row>
-    <row r="882" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A882" t="s">
         <v>38</v>
       </c>
@@ -25904,7 +25780,7 @@
         <v>1478731.1339752299</v>
       </c>
     </row>
-    <row r="883" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A883" t="s">
         <v>38</v>
       </c>
@@ -25924,7 +25800,7 @@
         <v>893627.08894131298</v>
       </c>
     </row>
-    <row r="884" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A884" t="s">
         <v>43</v>
       </c>
@@ -25944,7 +25820,7 @@
         <v>3745292.61150365</v>
       </c>
     </row>
-    <row r="885" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A885" t="s">
         <v>43</v>
       </c>
@@ -25964,7 +25840,7 @@
         <v>3913542.1959118498</v>
       </c>
     </row>
-    <row r="886" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A886" t="s">
         <v>43</v>
       </c>
@@ -25984,7 +25860,7 @@
         <v>3788001.0235920199</v>
       </c>
     </row>
-    <row r="887" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A887" t="s">
         <v>43</v>
       </c>
@@ -26004,7 +25880,7 @@
         <v>3576146.3514422602</v>
       </c>
     </row>
-    <row r="888" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A888" t="s">
         <v>43</v>
       </c>
@@ -26024,7 +25900,7 @@
         <v>6022494.9352980498</v>
       </c>
     </row>
-    <row r="889" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A889" t="s">
         <v>43</v>
       </c>
@@ -26044,7 +25920,7 @@
         <v>4272152.1043191897</v>
       </c>
     </row>
-    <row r="890" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A890" t="s">
         <v>43</v>
       </c>
@@ -26064,7 +25940,7 @@
         <v>2436966.2195611498</v>
       </c>
     </row>
-    <row r="891" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A891" t="s">
         <v>44</v>
       </c>
@@ -26084,7 +25960,7 @@
         <v>4392922.6008212604</v>
       </c>
     </row>
-    <row r="892" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A892" t="s">
         <v>44</v>
       </c>
@@ -26104,7 +25980,7 @@
         <v>2900949.9165622699</v>
       </c>
     </row>
-    <row r="893" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A893" t="s">
         <v>44</v>
       </c>
@@ -26124,7 +26000,7 @@
         <v>2649114.49951238</v>
       </c>
     </row>
-    <row r="894" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A894" t="s">
         <v>44</v>
       </c>
@@ -26144,7 +26020,7 @@
         <v>2372989.3622322902</v>
       </c>
     </row>
-    <row r="895" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A895" t="s">
         <v>44</v>
       </c>
@@ -26164,7 +26040,7 @@
         <v>3326822.0930527402</v>
       </c>
     </row>
-    <row r="896" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A896" t="s">
         <v>44</v>
       </c>
@@ -26184,7 +26060,7 @@
         <v>1317433.79705026</v>
       </c>
     </row>
-    <row r="897" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A897" t="s">
         <v>44</v>
       </c>
@@ -26204,7 +26080,7 @@
         <v>4178697.3444127501</v>
       </c>
     </row>
-    <row r="898" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A898" t="s">
         <v>44</v>
       </c>
@@ -26224,7 +26100,7 @@
         <v>1507230.61988843</v>
       </c>
     </row>
-    <row r="899" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A899" t="s">
         <v>44</v>
       </c>
@@ -26244,7 +26120,7 @@
         <v>6387931.6758292597</v>
       </c>
     </row>
-    <row r="900" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A900" t="s">
         <v>44</v>
       </c>
@@ -26264,7 +26140,7 @@
         <v>1071783.38191454</v>
       </c>
     </row>
-    <row r="901" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A901" t="s">
         <v>44</v>
       </c>
@@ -26284,7 +26160,7 @@
         <v>4237355.71391025</v>
       </c>
     </row>
-    <row r="902" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A902" t="s">
         <v>44</v>
       </c>
@@ -26304,7 +26180,7 @@
         <v>2328227.75467346</v>
       </c>
     </row>
-    <row r="903" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A903" t="s">
         <v>44</v>
       </c>
@@ -26324,7 +26200,7 @@
         <v>7052659.4882633397</v>
       </c>
     </row>
-    <row r="904" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A904" t="s">
         <v>44</v>
       </c>
@@ -26353,17 +26229,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50C6B2B5-6AB3-4816-99A5-0CE310DF5A07}">
   <dimension ref="A1:F42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="5" max="5" width="13.88671875" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -26371,7 +26247,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -26379,7 +26255,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>48</v>
       </c>
@@ -26387,7 +26263,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>47</v>
       </c>
@@ -26404,7 +26280,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>2017</v>
       </c>
@@ -26421,7 +26297,7 @@
         <v>347302799.18141562</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>2018</v>
       </c>
@@ -26438,7 +26314,7 @@
         <v>354522052.09476119</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>2019</v>
       </c>
@@ -26455,7 +26331,7 @@
         <v>543263014.02229393</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>2020</v>
       </c>
@@ -26472,7 +26348,7 @@
         <v>519549044.09934878</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>2021</v>
       </c>
@@ -26489,7 +26365,7 @@
         <v>635845743.79782748</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>2022</v>
       </c>
@@ -26505,12 +26381,9 @@
       <c r="E11" s="3">
         <v>669986245.77510929</v>
       </c>
-      <c r="F11" s="3">
-        <f>E11+(E11*-0.0418627619890395)</f>
-        <v>641938771.03229582</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>2023</v>
       </c>
@@ -26526,12 +26399,9 @@
       <c r="E12" s="3">
         <v>413560041.77863795</v>
       </c>
-      <c r="F12" s="3">
-        <f>E12+(E12*-0.0418627619890395)</f>
-        <v>396247276.1814816</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>46</v>
       </c>
@@ -26548,7 +26418,7 @@
         <v>3484028940.7493944</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
@@ -26556,7 +26426,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>2</v>
       </c>
@@ -26564,7 +26434,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>48</v>
       </c>
@@ -26572,7 +26442,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>47</v>
       </c>
@@ -26589,7 +26459,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>2017</v>
       </c>
@@ -26606,7 +26476,7 @@
         <v>42251531.928374939</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>2018</v>
       </c>
@@ -26623,7 +26493,7 @@
         <v>12533248.299764549</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>2019</v>
       </c>
@@ -26640,7 +26510,7 @@
         <v>16674331.30634181</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>2020</v>
       </c>
@@ -26657,7 +26527,7 @@
         <v>45903477.662385941</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>2021</v>
       </c>
@@ -26674,7 +26544,7 @@
         <v>9047634.9496976417</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>2022</v>
       </c>
@@ -26691,7 +26561,7 @@
         <v>31105316.88997731</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>2023</v>
       </c>
@@ -26708,7 +26578,7 @@
         <v>21125329.610565253</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>46</v>
       </c>
@@ -26725,7 +26595,7 @@
         <v>178640870.64710745</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>0</v>
       </c>
@@ -26733,7 +26603,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>2</v>
       </c>
@@ -26741,7 +26611,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>48</v>
       </c>
@@ -26749,7 +26619,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>47</v>
       </c>
@@ -26760,7 +26630,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>2017</v>
       </c>
@@ -26771,7 +26641,7 @@
         <v>7133905.4346014811</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>2018</v>
       </c>
@@ -26782,7 +26652,7 @@
         <v>4989357.4091276657</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>2019</v>
       </c>
@@ -26793,7 +26663,7 @@
         <v>17664622.985068053</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>2020</v>
       </c>
@@ -26804,7 +26674,7 @@
         <v>20806516.153342947</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>2021</v>
       </c>
@@ -26815,7 +26685,7 @@
         <v>29424769.892841175</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>2022</v>
       </c>
@@ -26826,7 +26696,7 @@
         <v>25544282.843620852</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>2023</v>
       </c>
@@ -26837,7 +26707,7 @@
         <v>25629477.453744736</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>46</v>
       </c>
@@ -26852,213 +26722,4 @@
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20DD2CFD-87D6-4158-9E96-626B05AFD8BB}">
-  <dimension ref="F6:K18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="6" max="6" width="19" customWidth="1"/>
-    <col min="7" max="7" width="35.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.140625" customWidth="1"/>
-    <col min="10" max="10" width="25.42578125" customWidth="1"/>
-    <col min="11" max="11" width="30.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="6" spans="6:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="6:11" x14ac:dyDescent="0.25">
-      <c r="F7" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="6:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F8" s="19"/>
-      <c r="G8" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="6:11" x14ac:dyDescent="0.25">
-      <c r="F9" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9" s="21">
-        <v>464407389</v>
-      </c>
-      <c r="H9" s="21">
-        <f>Planilha1!F11</f>
-        <v>641938771.03229582</v>
-      </c>
-      <c r="I9" s="22">
-        <f>Planilha1!F12</f>
-        <v>396247276.1814816</v>
-      </c>
-      <c r="J9" s="8">
-        <f>G9-H9</f>
-        <v>-177531382.03229582</v>
-      </c>
-      <c r="K9" s="8">
-        <f>G9-I9</f>
-        <v>68160112.8185184</v>
-      </c>
-    </row>
-    <row r="10" spans="6:11" x14ac:dyDescent="0.25">
-      <c r="F10" s="12"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="11">
-        <f>(J9/G9)*-100</f>
-        <v>38.227510207055687</v>
-      </c>
-      <c r="K10" s="11">
-        <f>(K9/G9)*-100</f>
-        <v>-14.676793357075205</v>
-      </c>
-    </row>
-    <row r="11" spans="6:11" x14ac:dyDescent="0.25">
-      <c r="F11" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="G11" s="14">
-        <v>25215124</v>
-      </c>
-      <c r="H11" s="14">
-        <f>GETPIVOTDATA("emission_tco2eq",Planilha1!$A$19,"year",2022)</f>
-        <v>31105316.88997731</v>
-      </c>
-      <c r="I11" s="16">
-        <f>GETPIVOTDATA("emission_tco2eq",Planilha1!$A$19,"year",2023)</f>
-        <v>21125329.610565253</v>
-      </c>
-      <c r="J11" s="8">
-        <f>G11-H11</f>
-        <v>-5890192.8899773099</v>
-      </c>
-      <c r="K11" s="8">
-        <f>G11-I11</f>
-        <v>4089794.3894347474</v>
-      </c>
-    </row>
-    <row r="12" spans="6:11" x14ac:dyDescent="0.25">
-      <c r="F12" s="12"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="11">
-        <f>(J11/G11)*-100</f>
-        <v>23.359761744488384</v>
-      </c>
-      <c r="K12" s="11">
-        <f>(K11/G11)*-100</f>
-        <v>-16.219608475590867</v>
-      </c>
-    </row>
-    <row r="13" spans="6:11" x14ac:dyDescent="0.25">
-      <c r="F13" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="G13" s="14">
-        <v>15892594</v>
-      </c>
-      <c r="H13" s="14">
-        <f>GETPIVOTDATA("emission_tco2eq",Planilha1!$A$33,"year",2022)</f>
-        <v>25544282.843620852</v>
-      </c>
-      <c r="I13" s="16">
-        <f>GETPIVOTDATA("emission_tco2eq",Planilha1!$A$33,"year",2023)</f>
-        <v>25629477.453744736</v>
-      </c>
-      <c r="J13" s="8">
-        <f>G13-H13</f>
-        <v>-9651688.8436208516</v>
-      </c>
-      <c r="K13" s="8">
-        <f>G13-I13</f>
-        <v>-9736883.4537447356</v>
-      </c>
-    </row>
-    <row r="14" spans="6:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F14" s="13"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="11">
-        <f>(J13/G13)*-100</f>
-        <v>60.730733092538905</v>
-      </c>
-      <c r="K14" s="11">
-        <f>(K13/G13)*-100</f>
-        <v>61.266797942140435</v>
-      </c>
-    </row>
-    <row r="15" spans="6:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="F15" s="9"/>
-    </row>
-    <row r="17" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H17" s="3">
-        <f>H11+H13</f>
-        <v>56649599.733598158</v>
-      </c>
-      <c r="I17" s="3">
-        <f>I11+I13</f>
-        <v>46754807.064309984</v>
-      </c>
-    </row>
-    <row r="18" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H18" s="10">
-        <f>H17/H9*100</f>
-        <v>8.8247668297866575</v>
-      </c>
-      <c r="I18" s="10">
-        <f>I17/I9*100</f>
-        <v>11.799401503745919</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="I11:I12"/>
-  </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
 </file>